--- a/research/traditional_assets/database/data/switzerland/switzerland_shipbuilding_marine.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_shipbuilding_marine.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08301470951614079</v>
+        <v>0.08293193804024722</v>
       </c>
       <c r="C2">
-        <v>29589.52515461833</v>
+        <v>29340.47672223961</v>
       </c>
       <c r="D2">
-        <v>28493.32515461833</v>
+        <v>28544.36122039267</v>
       </c>
       <c r="E2">
-        <v>-2877.14981530561</v>
+        <v>-2577.065317152554</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>300.0844981530561</v>
       </c>
       <c r="G2">
         <v>1096.2</v>
@@ -1457,28 +1457,28 @@
         <v>1162.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>15.09425025709872</v>
       </c>
       <c r="N2">
-        <v>1162.7</v>
+        <v>1147.605749742901</v>
       </c>
       <c r="O2">
-        <v>169.7542</v>
+        <v>167.5504394624636</v>
       </c>
       <c r="P2">
-        <v>992.9458000000002</v>
+        <v>980.0553102804379</v>
       </c>
       <c r="Q2">
-        <v>1953.0458</v>
+        <v>1940.155310280438</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08301470951614079</v>
+        <v>0.0833357333739871</v>
       </c>
       <c r="T2">
-        <v>0.8594621135367391</v>
+        <v>0.8668760594454297</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>77.02933104962868</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08293193804024722</v>
+        <v>0.08284916656435366</v>
       </c>
       <c r="C3">
-        <v>29340.47672223961</v>
+        <v>29091.61144530254</v>
       </c>
       <c r="D3">
-        <v>28544.36122039267</v>
+        <v>28595.58044160865</v>
       </c>
       <c r="E3">
-        <v>-2577.065317152554</v>
+        <v>-2276.980818999498</v>
       </c>
       <c r="F3">
-        <v>300.0844981530561</v>
+        <v>600.1689963061121</v>
       </c>
       <c r="G3">
         <v>1096.2</v>
@@ -1539,28 +1539,28 @@
         <v>1162.7</v>
       </c>
       <c r="M3">
-        <v>15.09425025709872</v>
+        <v>30.18850051419744</v>
       </c>
       <c r="N3">
-        <v>1147.605749742901</v>
+        <v>1132.511499485803</v>
       </c>
       <c r="O3">
-        <v>167.5504394624636</v>
+        <v>165.3466789249272</v>
       </c>
       <c r="P3">
-        <v>980.0553102804379</v>
+        <v>967.1648205608757</v>
       </c>
       <c r="Q3">
-        <v>1940.155310280438</v>
+        <v>1927.264820560876</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0833357333739871</v>
+        <v>0.08366330873913638</v>
       </c>
       <c r="T3">
-        <v>0.8668760594454297</v>
+        <v>0.874441310372665</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>77.02933104962868</v>
+        <v>38.51466552481435</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08284916656435366</v>
+        <v>0.08276639508846008</v>
       </c>
       <c r="C4">
-        <v>29091.61144530254</v>
+        <v>28842.9303115268</v>
       </c>
       <c r="D4">
-        <v>28595.58044160865</v>
+        <v>28646.98380598597</v>
       </c>
       <c r="E4">
-        <v>-2276.980818999498</v>
+        <v>-1976.896320846442</v>
       </c>
       <c r="F4">
-        <v>600.1689963061121</v>
+        <v>900.2534944591682</v>
       </c>
       <c r="G4">
         <v>1096.2</v>
@@ -1621,28 +1621,28 @@
         <v>1162.7</v>
       </c>
       <c r="M4">
-        <v>30.18850051419744</v>
+        <v>45.28275077129616</v>
       </c>
       <c r="N4">
-        <v>1132.511499485803</v>
+        <v>1117.417249228704</v>
       </c>
       <c r="O4">
-        <v>165.3466789249272</v>
+        <v>163.1429183873908</v>
       </c>
       <c r="P4">
-        <v>967.1648205608757</v>
+        <v>954.2743308413134</v>
       </c>
       <c r="Q4">
-        <v>1927.264820560876</v>
+        <v>1914.374330841313</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08366330873913638</v>
+        <v>0.08399763823552586</v>
       </c>
       <c r="T4">
-        <v>0.874441310372665</v>
+        <v>0.8821625458551011</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>38.51466552481435</v>
+        <v>25.67644368320957</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08276639508846008</v>
+        <v>0.08268362361256654</v>
       </c>
       <c r="C5">
-        <v>28842.9303115268</v>
+        <v>28594.43431574694</v>
       </c>
       <c r="D5">
-        <v>28646.98380598597</v>
+        <v>28698.57230835916</v>
       </c>
       <c r="E5">
-        <v>-1976.896320846442</v>
+        <v>-1676.811822693386</v>
       </c>
       <c r="F5">
-        <v>900.2534944591682</v>
+        <v>1200.337992612224</v>
       </c>
       <c r="G5">
         <v>1096.2</v>
@@ -1703,28 +1703,28 @@
         <v>1162.7</v>
       </c>
       <c r="M5">
-        <v>45.28275077129616</v>
+        <v>60.37700102839488</v>
       </c>
       <c r="N5">
-        <v>1117.417249228704</v>
+        <v>1102.322998971605</v>
       </c>
       <c r="O5">
-        <v>163.1429183873908</v>
+        <v>160.9391578498544</v>
       </c>
       <c r="P5">
-        <v>954.2743308413134</v>
+        <v>941.3838411217509</v>
       </c>
       <c r="Q5">
-        <v>1914.374330841313</v>
+        <v>1901.483841121751</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08399763823552586</v>
+        <v>0.0843389329297568</v>
       </c>
       <c r="T5">
-        <v>0.8821625458551011</v>
+        <v>0.890044640410088</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>25.67644368320957</v>
+        <v>19.25733276240717</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08268362361256654</v>
+        <v>0.08260085213667297</v>
       </c>
       <c r="C6">
-        <v>28594.43431574694</v>
+        <v>28346.12445997662</v>
       </c>
       <c r="D6">
-        <v>28698.57230835916</v>
+        <v>28750.3469507419</v>
       </c>
       <c r="E6">
-        <v>-1676.811822693386</v>
+        <v>-1376.727324540329</v>
       </c>
       <c r="F6">
-        <v>1200.337992612224</v>
+        <v>1500.422490765281</v>
       </c>
       <c r="G6">
         <v>1096.2</v>
@@ -1785,28 +1785,28 @@
         <v>1162.7</v>
       </c>
       <c r="M6">
-        <v>60.37700102839488</v>
+        <v>75.47125128549361</v>
       </c>
       <c r="N6">
-        <v>1102.322998971605</v>
+        <v>1087.228748714507</v>
       </c>
       <c r="O6">
-        <v>160.9391578498544</v>
+        <v>158.735397312318</v>
       </c>
       <c r="P6">
-        <v>941.3838411217509</v>
+        <v>928.4933514021888</v>
       </c>
       <c r="Q6">
-        <v>1901.483841121751</v>
+        <v>1888.593351402189</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0843389329297568</v>
+        <v>0.08468741277544523</v>
       </c>
       <c r="T6">
-        <v>0.890044640410088</v>
+        <v>0.8980926737978114</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.25733276240717</v>
+        <v>15.40586620992574</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08260085213667297</v>
+        <v>0.0825180806607794</v>
       </c>
       <c r="C7">
-        <v>28346.12445997662</v>
+        <v>28098.0017534734</v>
       </c>
       <c r="D7">
-        <v>28750.3469507419</v>
+        <v>28802.30874239173</v>
       </c>
       <c r="E7">
-        <v>-1376.727324540329</v>
+        <v>-1076.642826387273</v>
       </c>
       <c r="F7">
-        <v>1500.422490765281</v>
+        <v>1800.506988918337</v>
       </c>
       <c r="G7">
         <v>1096.2</v>
@@ -1867,28 +1867,28 @@
         <v>1162.7</v>
       </c>
       <c r="M7">
-        <v>75.47125128549361</v>
+        <v>90.56550154259233</v>
       </c>
       <c r="N7">
-        <v>1087.228748714507</v>
+        <v>1072.134498457408</v>
       </c>
       <c r="O7">
-        <v>158.735397312318</v>
+        <v>156.5316367747816</v>
       </c>
       <c r="P7">
-        <v>928.4933514021888</v>
+        <v>915.6028616826264</v>
       </c>
       <c r="Q7">
-        <v>1888.593351402189</v>
+        <v>1875.702861682626</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08468741277544523</v>
+        <v>0.08504330708593554</v>
       </c>
       <c r="T7">
-        <v>0.8980926737978114</v>
+        <v>0.9063119419384652</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>15.40586620992574</v>
+        <v>12.83822184160478</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0825180806607794</v>
+        <v>0.08243530918488584</v>
       </c>
       <c r="C8">
-        <v>28098.0017534734</v>
+        <v>27850.06721280434</v>
       </c>
       <c r="D8">
-        <v>28802.30874239173</v>
+        <v>28854.45869987573</v>
       </c>
       <c r="E8">
-        <v>-1076.642826387274</v>
+        <v>-776.5583282342177</v>
       </c>
       <c r="F8">
-        <v>1800.506988918336</v>
+        <v>2100.591487071392</v>
       </c>
       <c r="G8">
         <v>1096.2</v>
@@ -1949,28 +1949,28 @@
         <v>1162.7</v>
       </c>
       <c r="M8">
-        <v>90.56550154259232</v>
+        <v>105.659751799691</v>
       </c>
       <c r="N8">
-        <v>1072.134498457408</v>
+        <v>1057.040248200309</v>
       </c>
       <c r="O8">
-        <v>156.5316367747816</v>
+        <v>154.3278762372451</v>
       </c>
       <c r="P8">
-        <v>915.6028616826264</v>
+        <v>902.712371963064</v>
       </c>
       <c r="Q8">
-        <v>1875.702861682626</v>
+        <v>1862.812371963064</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08504330708593554</v>
+        <v>0.08540685503751165</v>
       </c>
       <c r="T8">
-        <v>0.9063119419384652</v>
+        <v>0.9147079685337566</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>12.83822184160478</v>
+        <v>11.00419014994696</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08243530918488583</v>
+        <v>0.08235253770899227</v>
       </c>
       <c r="C9">
-        <v>27850.06721280435</v>
+        <v>27602.32186191236</v>
       </c>
       <c r="D9">
-        <v>28854.45869987574</v>
+        <v>28906.7978471368</v>
       </c>
       <c r="E9">
-        <v>-776.5583282342172</v>
+        <v>-476.4738300811614</v>
       </c>
       <c r="F9">
-        <v>2100.591487071393</v>
+        <v>2400.675985224449</v>
       </c>
       <c r="G9">
         <v>1096.2</v>
@@ -2031,28 +2031,28 @@
         <v>1162.7</v>
       </c>
       <c r="M9">
-        <v>105.6597517996911</v>
+        <v>120.7540020567898</v>
       </c>
       <c r="N9">
-        <v>1057.040248200309</v>
+        <v>1041.945997943211</v>
       </c>
       <c r="O9">
-        <v>154.3278762372451</v>
+        <v>152.1241156997087</v>
       </c>
       <c r="P9">
-        <v>902.712371963064</v>
+        <v>889.8218822435019</v>
       </c>
       <c r="Q9">
-        <v>1862.812371963064</v>
+        <v>1849.921882243502</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08540685503751165</v>
+        <v>0.08577830620542638</v>
       </c>
       <c r="T9">
-        <v>0.9147079685337566</v>
+        <v>0.9232865174463369</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.00419014994695</v>
+        <v>9.628666381203587</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08235253770899227</v>
+        <v>0.08238505623309869</v>
       </c>
       <c r="C10">
-        <v>27602.32186191236</v>
+        <v>27281.6521944766</v>
       </c>
       <c r="D10">
-        <v>28906.7978471368</v>
+        <v>28886.2126778541</v>
       </c>
       <c r="E10">
-        <v>-476.4738300811614</v>
+        <v>-176.3893319281055</v>
       </c>
       <c r="F10">
-        <v>2400.675985224449</v>
+        <v>2700.760483377504</v>
       </c>
       <c r="G10">
         <v>1096.2</v>
@@ -2113,45 +2113,45 @@
         <v>1162.7</v>
       </c>
       <c r="M10">
-        <v>120.7540020567898</v>
+        <v>139.8993930389547</v>
       </c>
       <c r="N10">
-        <v>1041.945997943211</v>
+        <v>1022.800606961046</v>
       </c>
       <c r="O10">
-        <v>152.1241156997087</v>
+        <v>149.3288886163126</v>
       </c>
       <c r="P10">
-        <v>889.8218822435019</v>
+        <v>873.4717183447329</v>
       </c>
       <c r="Q10">
-        <v>1849.921882243502</v>
+        <v>1833.571718344733</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08577830620542638</v>
+        <v>0.08615792113527329</v>
       </c>
       <c r="T10">
-        <v>0.9232865174463369</v>
+        <v>0.9320536058954574</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.146</v>
       </c>
       <c r="W10">
-        <v>0.0429562</v>
+        <v>0.0442372</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>9.628666381203587</v>
+        <v>8.310972440575554</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08238505623309869</v>
+        <v>0.08231509475720514</v>
       </c>
       <c r="C11">
-        <v>27281.6521944766</v>
+        <v>27025.89171039854</v>
       </c>
       <c r="D11">
-        <v>28886.2126778541</v>
+        <v>28930.5366919291</v>
       </c>
       <c r="E11">
-        <v>-176.3893319281055</v>
+        <v>123.6951662249508</v>
       </c>
       <c r="F11">
-        <v>2700.760483377504</v>
+        <v>3000.844981530561</v>
       </c>
       <c r="G11">
         <v>1096.2</v>
@@ -2195,28 +2195,28 @@
         <v>1162.7</v>
       </c>
       <c r="M11">
-        <v>139.8993930389547</v>
+        <v>155.4437700432831</v>
       </c>
       <c r="N11">
-        <v>1022.800606961046</v>
+        <v>1007.256229956717</v>
       </c>
       <c r="O11">
-        <v>149.3288886163126</v>
+        <v>147.0594095736807</v>
       </c>
       <c r="P11">
-        <v>873.4717183447329</v>
+        <v>860.1968203830365</v>
       </c>
       <c r="Q11">
-        <v>1833.571718344733</v>
+        <v>1820.296820383036</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08615792113527329</v>
+        <v>0.08654597195245015</v>
       </c>
       <c r="T11">
-        <v>0.9320536058954574</v>
+        <v>0.9410155185323362</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.310972440575554</v>
+        <v>7.479875196517998</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08231509475720514</v>
+        <v>0.08224513328131157</v>
       </c>
       <c r="C12">
-        <v>27025.89171039854</v>
+        <v>26770.26745999413</v>
       </c>
       <c r="D12">
-        <v>28930.5366919291</v>
+        <v>28974.99693967775</v>
       </c>
       <c r="E12">
-        <v>123.6951662249512</v>
+        <v>423.7796643780071</v>
       </c>
       <c r="F12">
-        <v>3000.844981530561</v>
+        <v>3300.929479683617</v>
       </c>
       <c r="G12">
         <v>1096.2</v>
@@ -2277,28 +2277,28 @@
         <v>1162.7</v>
       </c>
       <c r="M12">
-        <v>155.4437700432831</v>
+        <v>170.9881470476114</v>
       </c>
       <c r="N12">
-        <v>1007.256229956717</v>
+        <v>991.7118529523889</v>
       </c>
       <c r="O12">
-        <v>147.0594095736807</v>
+        <v>144.7899305310488</v>
       </c>
       <c r="P12">
-        <v>860.1968203830365</v>
+        <v>846.9219224213401</v>
       </c>
       <c r="Q12">
-        <v>1820.296820383036</v>
+        <v>1807.02192242134</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08654597195245015</v>
+        <v>0.08694274301270963</v>
       </c>
       <c r="T12">
-        <v>0.9410155185323362</v>
+        <v>0.9501788224644259</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.479875196517998</v>
+        <v>6.799886542289088</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08224513328131157</v>
+        <v>0.08234938780541801</v>
       </c>
       <c r="C13">
-        <v>26770.26745999413</v>
+        <v>26403.97940837595</v>
       </c>
       <c r="D13">
-        <v>28974.99693967775</v>
+        <v>28908.79338621262</v>
       </c>
       <c r="E13">
-        <v>423.7796643780071</v>
+        <v>723.8641625310629</v>
       </c>
       <c r="F13">
-        <v>3300.929479683617</v>
+        <v>3601.013977836673</v>
       </c>
       <c r="G13">
         <v>1096.2</v>
@@ -2359,45 +2359,45 @@
         <v>1162.7</v>
       </c>
       <c r="M13">
-        <v>170.9881470476114</v>
+        <v>192.654247814262</v>
       </c>
       <c r="N13">
-        <v>991.7118529523889</v>
+        <v>970.0457521857383</v>
       </c>
       <c r="O13">
-        <v>144.7899305310488</v>
+        <v>141.6266798191178</v>
       </c>
       <c r="P13">
-        <v>846.9219224213401</v>
+        <v>828.4190723666204</v>
       </c>
       <c r="Q13">
-        <v>1807.02192242134</v>
+        <v>1788.519072366621</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08694274301270963</v>
+        <v>0.0873485315970659</v>
       </c>
       <c r="T13">
-        <v>0.9501788224644259</v>
+        <v>0.9595503833040628</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.146</v>
       </c>
       <c r="W13">
-        <v>0.0442372</v>
+        <v>0.045689</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.799886542289088</v>
+        <v>6.03516409937122</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08234938780541801</v>
+        <v>0.08238276032952443</v>
       </c>
       <c r="C14">
-        <v>26403.97940837595</v>
+        <v>26082.7666134872</v>
       </c>
       <c r="D14">
-        <v>28908.79338621262</v>
+        <v>28887.66508947693</v>
       </c>
       <c r="E14">
-        <v>723.8641625310629</v>
+        <v>1023.948660684119</v>
       </c>
       <c r="F14">
-        <v>3601.013977836673</v>
+        <v>3901.098475989729</v>
       </c>
       <c r="G14">
         <v>1096.2</v>
@@ -2441,45 +2441,45 @@
         <v>1162.7</v>
       </c>
       <c r="M14">
-        <v>192.654247814262</v>
+        <v>211.8296472462423</v>
       </c>
       <c r="N14">
-        <v>970.0457521857383</v>
+        <v>950.870352753758</v>
       </c>
       <c r="O14">
-        <v>141.6266798191178</v>
+        <v>138.8270715020487</v>
       </c>
       <c r="P14">
-        <v>828.4190723666204</v>
+        <v>812.0432812517093</v>
       </c>
       <c r="Q14">
-        <v>1788.519072366621</v>
+        <v>1772.143281251709</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0873485315970659</v>
+        <v>0.0877636486546258</v>
       </c>
       <c r="T14">
-        <v>0.9595503833040628</v>
+        <v>0.9691373823239215</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.146</v>
       </c>
       <c r="W14">
-        <v>0.045689</v>
+        <v>0.0463722</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.03516409937122</v>
+        <v>5.488844527264942</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08238276032952443</v>
+        <v>0.08233414885363087</v>
       </c>
       <c r="C15">
-        <v>26082.7666134872</v>
+        <v>25813.46854372337</v>
       </c>
       <c r="D15">
-        <v>28887.66508947693</v>
+        <v>28918.45151786616</v>
       </c>
       <c r="E15">
-        <v>1023.948660684119</v>
+        <v>1324.033158837176</v>
       </c>
       <c r="F15">
-        <v>3901.098475989729</v>
+        <v>4201.182974142785</v>
       </c>
       <c r="G15">
         <v>1096.2</v>
@@ -2523,28 +2523,28 @@
         <v>1162.7</v>
       </c>
       <c r="M15">
-        <v>211.8296472462423</v>
+        <v>228.1242354959533</v>
       </c>
       <c r="N15">
-        <v>950.870352753758</v>
+        <v>934.575764504047</v>
       </c>
       <c r="O15">
-        <v>138.8270715020487</v>
+        <v>136.4480616175909</v>
       </c>
       <c r="P15">
-        <v>812.0432812517093</v>
+        <v>798.1277028864562</v>
       </c>
       <c r="Q15">
-        <v>1772.143281251709</v>
+        <v>1758.227702886456</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.0877636486546258</v>
+        <v>0.0881884195972452</v>
       </c>
       <c r="T15">
-        <v>0.9691373823239215</v>
+        <v>0.9789473348093582</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.488844527264942</v>
+        <v>5.096784203888874</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08233414885363087</v>
+        <v>0.08228553737773732</v>
       </c>
       <c r="C16">
-        <v>25813.46854372337</v>
+        <v>25544.23616395907</v>
       </c>
       <c r="D16">
-        <v>28918.45151786616</v>
+        <v>28949.30363625491</v>
       </c>
       <c r="E16">
-        <v>1324.033158837176</v>
+        <v>1624.117656990232</v>
       </c>
       <c r="F16">
-        <v>4201.182974142785</v>
+        <v>4501.267472295842</v>
       </c>
       <c r="G16">
         <v>1096.2</v>
@@ -2605,28 +2605,28 @@
         <v>1162.7</v>
       </c>
       <c r="M16">
-        <v>228.1242354959533</v>
+        <v>244.4188237456642</v>
       </c>
       <c r="N16">
-        <v>934.575764504047</v>
+        <v>918.2811762543361</v>
       </c>
       <c r="O16">
-        <v>136.4480616175909</v>
+        <v>134.0690517331331</v>
       </c>
       <c r="P16">
-        <v>798.1277028864562</v>
+        <v>784.212124521203</v>
       </c>
       <c r="Q16">
-        <v>1758.227702886456</v>
+        <v>1744.312124521203</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0881884195972452</v>
+        <v>0.0886231851502792</v>
       </c>
       <c r="T16">
-        <v>0.9789473348093582</v>
+        <v>0.9889881097062171</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.096784203888874</v>
+        <v>4.756998590296282</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08228553737773732</v>
+        <v>0.08223692590184374</v>
       </c>
       <c r="C17">
-        <v>25544.23616395907</v>
+        <v>25275.0696846662</v>
       </c>
       <c r="D17">
-        <v>28949.30363625491</v>
+        <v>28980.22165511509</v>
       </c>
       <c r="E17">
-        <v>1624.117656990231</v>
+        <v>1924.202155143287</v>
       </c>
       <c r="F17">
-        <v>4501.267472295841</v>
+        <v>4801.351970448897</v>
       </c>
       <c r="G17">
         <v>1096.2</v>
@@ -2687,28 +2687,28 @@
         <v>1162.7</v>
       </c>
       <c r="M17">
-        <v>244.4188237456642</v>
+        <v>260.7134119953751</v>
       </c>
       <c r="N17">
-        <v>918.2811762543361</v>
+        <v>901.9865880046252</v>
       </c>
       <c r="O17">
-        <v>134.0690517331331</v>
+        <v>131.6900418486753</v>
       </c>
       <c r="P17">
-        <v>784.212124521203</v>
+        <v>770.29654615595</v>
       </c>
       <c r="Q17">
-        <v>1744.312124521203</v>
+        <v>1730.39654615595</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0886231851502792</v>
+        <v>0.0890683022640997</v>
       </c>
       <c r="T17">
-        <v>0.9889881097062171</v>
+        <v>0.9992679506720487</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.756998590296284</v>
+        <v>4.459686178402766</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08223692590184374</v>
+        <v>0.08233349442595017</v>
       </c>
       <c r="C18">
-        <v>25275.0696846662</v>
+        <v>24913.62995647902</v>
       </c>
       <c r="D18">
-        <v>28980.22165511509</v>
+        <v>28918.86642508098</v>
       </c>
       <c r="E18">
-        <v>1924.202155143287</v>
+        <v>2224.286653296344</v>
       </c>
       <c r="F18">
-        <v>4801.351970448897</v>
+        <v>5101.436468601953</v>
       </c>
       <c r="G18">
         <v>1096.2</v>
@@ -2769,45 +2769,45 @@
         <v>1162.7</v>
       </c>
       <c r="M18">
-        <v>260.7134119953751</v>
+        <v>282.109436713688</v>
       </c>
       <c r="N18">
-        <v>901.9865880046252</v>
+        <v>880.5905632863123</v>
       </c>
       <c r="O18">
-        <v>131.6900418486753</v>
+        <v>128.5662222398016</v>
       </c>
       <c r="P18">
-        <v>770.29654615595</v>
+        <v>752.0243410465107</v>
       </c>
       <c r="Q18">
-        <v>1730.39654615595</v>
+        <v>1712.124341046511</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0890683022640997</v>
+        <v>0.08952414509150623</v>
       </c>
       <c r="T18">
-        <v>0.9992679506720487</v>
+        <v>1.009795498649105</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.146</v>
       </c>
       <c r="W18">
-        <v>0.0463722</v>
+        <v>0.0472262</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.459686178402766</v>
+        <v>4.121450219972687</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08233349442595017</v>
+        <v>0.08229342295005661</v>
       </c>
       <c r="C19">
-        <v>24913.62995647902</v>
+        <v>24638.97348146369</v>
       </c>
       <c r="D19">
-        <v>28918.86642508098</v>
+        <v>28944.2944482187</v>
       </c>
       <c r="E19">
-        <v>2224.286653296344</v>
+        <v>2524.3711514494</v>
       </c>
       <c r="F19">
-        <v>5101.436468601953</v>
+        <v>5401.52096675501</v>
       </c>
       <c r="G19">
         <v>1096.2</v>
@@ -2851,28 +2851,28 @@
         <v>1162.7</v>
       </c>
       <c r="M19">
-        <v>282.109436713688</v>
+        <v>298.704109461552</v>
       </c>
       <c r="N19">
-        <v>880.5905632863123</v>
+        <v>863.9958905384483</v>
       </c>
       <c r="O19">
-        <v>128.5662222398016</v>
+        <v>126.1434000186134</v>
       </c>
       <c r="P19">
-        <v>752.0243410465107</v>
+        <v>737.8524905198349</v>
       </c>
       <c r="Q19">
-        <v>1712.124341046511</v>
+        <v>1697.952490519835</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08952414509150623</v>
+        <v>0.0899911060366544</v>
       </c>
       <c r="T19">
-        <v>1.009795498649105</v>
+        <v>1.020579816089016</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.121450219972687</v>
+        <v>3.892480763307538</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08229342295005662</v>
+        <v>0.08225335147416306</v>
       </c>
       <c r="C20">
-        <v>24638.97348146369</v>
+        <v>24364.36176293262</v>
       </c>
       <c r="D20">
-        <v>28944.29444821869</v>
+        <v>28969.76722784069</v>
       </c>
       <c r="E20">
-        <v>2524.371151449399</v>
+        <v>2824.455649602456</v>
       </c>
       <c r="F20">
-        <v>5401.520966755009</v>
+        <v>5701.605464908066</v>
       </c>
       <c r="G20">
         <v>1096.2</v>
@@ -2933,28 +2933,28 @@
         <v>1162.7</v>
       </c>
       <c r="M20">
-        <v>298.704109461552</v>
+        <v>315.2987822094161</v>
       </c>
       <c r="N20">
-        <v>863.9958905384483</v>
+        <v>847.4012177905843</v>
       </c>
       <c r="O20">
-        <v>126.1434000186134</v>
+        <v>123.7205777974253</v>
       </c>
       <c r="P20">
-        <v>737.8524905198349</v>
+        <v>723.6806399931589</v>
       </c>
       <c r="Q20">
-        <v>1697.952490519835</v>
+        <v>1683.780639993159</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0899911060366544</v>
+        <v>0.09046959688168278</v>
       </c>
       <c r="T20">
-        <v>1.020579816089016</v>
+        <v>1.031630412971889</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.892480763307538</v>
+        <v>3.687613354712404</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08225335147416306</v>
+        <v>0.0822132799982695</v>
       </c>
       <c r="C21">
-        <v>24364.36176293262</v>
+        <v>24089.79491915539</v>
       </c>
       <c r="D21">
-        <v>28969.76722784069</v>
+        <v>28995.28488221651</v>
       </c>
       <c r="E21">
-        <v>2824.455649602456</v>
+        <v>3124.540147755512</v>
       </c>
       <c r="F21">
-        <v>5701.605464908066</v>
+        <v>6001.689963061122</v>
       </c>
       <c r="G21">
         <v>1096.2</v>
@@ -3015,28 +3015,28 @@
         <v>1162.7</v>
       </c>
       <c r="M21">
-        <v>315.2987822094161</v>
+        <v>331.8934549572801</v>
       </c>
       <c r="N21">
-        <v>847.4012177905843</v>
+        <v>830.8065450427202</v>
       </c>
       <c r="O21">
-        <v>123.7205777974253</v>
+        <v>121.2977555762372</v>
       </c>
       <c r="P21">
-        <v>723.6806399931589</v>
+        <v>709.5087894664831</v>
       </c>
       <c r="Q21">
-        <v>1683.780639993159</v>
+        <v>1669.608789466483</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09046959688168278</v>
+        <v>0.09096004999783686</v>
       </c>
       <c r="T21">
-        <v>1.031630412971889</v>
+        <v>1.042957274776833</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.687613354712404</v>
+        <v>3.503232686976783</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0822132799982695</v>
+        <v>0.08217320852237592</v>
       </c>
       <c r="C22">
-        <v>24089.79491915539</v>
+        <v>23815.27306881862</v>
       </c>
       <c r="D22">
-        <v>28995.28488221651</v>
+        <v>29020.8475300328</v>
       </c>
       <c r="E22">
-        <v>3124.540147755512</v>
+        <v>3424.624645908569</v>
       </c>
       <c r="F22">
-        <v>6001.689963061122</v>
+        <v>6301.774461214179</v>
       </c>
       <c r="G22">
         <v>1096.2</v>
@@ -3097,28 +3097,28 @@
         <v>1162.7</v>
       </c>
       <c r="M22">
-        <v>331.8934549572801</v>
+        <v>348.4881277051441</v>
       </c>
       <c r="N22">
-        <v>830.8065450427202</v>
+        <v>814.2118722948562</v>
       </c>
       <c r="O22">
-        <v>121.2977555762372</v>
+        <v>118.874933355049</v>
       </c>
       <c r="P22">
-        <v>709.5087894664831</v>
+        <v>695.3369389398072</v>
       </c>
       <c r="Q22">
-        <v>1669.608789466483</v>
+        <v>1655.436938939807</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09096004999783686</v>
+        <v>0.09146291964857711</v>
       </c>
       <c r="T22">
-        <v>1.042957274776833</v>
+        <v>1.054570892576839</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.503232686976783</v>
+        <v>3.336412082835031</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08217320852237592</v>
+        <v>0.08213313704648234</v>
       </c>
       <c r="C23">
-        <v>23815.27306881862</v>
+        <v>23540.79633102784</v>
       </c>
       <c r="D23">
-        <v>29020.8475300328</v>
+        <v>29046.45529039508</v>
       </c>
       <c r="E23">
-        <v>3424.624645908568</v>
+        <v>3724.709144061624</v>
       </c>
       <c r="F23">
-        <v>6301.774461214178</v>
+        <v>6601.858959367234</v>
       </c>
       <c r="G23">
         <v>1096.2</v>
@@ -3179,28 +3179,28 @@
         <v>1162.7</v>
       </c>
       <c r="M23">
-        <v>348.4881277051441</v>
+        <v>365.0828004530081</v>
       </c>
       <c r="N23">
-        <v>814.2118722948562</v>
+        <v>797.6171995469922</v>
       </c>
       <c r="O23">
-        <v>118.874933355049</v>
+        <v>116.4521111338609</v>
       </c>
       <c r="P23">
-        <v>695.3369389398072</v>
+        <v>681.1650884131313</v>
       </c>
       <c r="Q23">
-        <v>1655.436938939807</v>
+        <v>1641.265088413131</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09146291964857711</v>
+        <v>0.09197868339292609</v>
       </c>
       <c r="T23">
-        <v>1.054570892576839</v>
+        <v>1.06648229544864</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.336412082835032</v>
+        <v>3.184756988160712</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08213313704648234</v>
+        <v>0.08209306557058879</v>
       </c>
       <c r="C24">
-        <v>23540.79633102784</v>
+        <v>23266.36482530935</v>
       </c>
       <c r="D24">
-        <v>29046.45529039508</v>
+        <v>29072.10828282963</v>
       </c>
       <c r="E24">
-        <v>3724.709144061624</v>
+        <v>4024.79364221468</v>
       </c>
       <c r="F24">
-        <v>6601.858959367234</v>
+        <v>6901.94345752029</v>
       </c>
       <c r="G24">
         <v>1096.2</v>
@@ -3261,28 +3261,28 @@
         <v>1162.7</v>
       </c>
       <c r="M24">
-        <v>365.0828004530081</v>
+        <v>381.6774732008721</v>
       </c>
       <c r="N24">
-        <v>797.6171995469922</v>
+        <v>781.0225267991282</v>
       </c>
       <c r="O24">
-        <v>116.4521111338609</v>
+        <v>114.0292889126727</v>
       </c>
       <c r="P24">
-        <v>681.1650884131313</v>
+        <v>666.9932378864555</v>
       </c>
       <c r="Q24">
-        <v>1641.265088413131</v>
+        <v>1627.093237886455</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09197868339292609</v>
+        <v>0.09250784359816726</v>
       </c>
       <c r="T24">
-        <v>1.06648229544864</v>
+        <v>1.07870308540802</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.184756988160712</v>
+        <v>3.04628929302329</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08209306557058879</v>
+        <v>0.08256539409469521</v>
       </c>
       <c r="C25">
-        <v>23266.36482530935</v>
+        <v>22666.75566385488</v>
       </c>
       <c r="D25">
-        <v>29072.10828282963</v>
+        <v>28772.58361952823</v>
       </c>
       <c r="E25">
-        <v>4024.79364221468</v>
+        <v>4324.878140367737</v>
       </c>
       <c r="F25">
-        <v>6901.94345752029</v>
+        <v>7202.027955673347</v>
       </c>
       <c r="G25">
         <v>1096.2</v>
@@ -3343,45 +3343,45 @@
         <v>1162.7</v>
       </c>
       <c r="M25">
-        <v>381.6774732008721</v>
+        <v>416.2772158379195</v>
       </c>
       <c r="N25">
-        <v>781.0225267991282</v>
+        <v>746.4227841620808</v>
       </c>
       <c r="O25">
-        <v>114.0292889126727</v>
+        <v>108.9777264876638</v>
       </c>
       <c r="P25">
-        <v>666.9932378864555</v>
+        <v>637.4450576744171</v>
       </c>
       <c r="Q25">
-        <v>1627.093237886455</v>
+        <v>1597.545057674417</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09250784359816726</v>
+        <v>0.09305092907196739</v>
       </c>
       <c r="T25">
-        <v>1.07870308540802</v>
+        <v>1.091245475103173</v>
       </c>
       <c r="U25">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.146</v>
       </c>
       <c r="W25">
-        <v>0.0472262</v>
+        <v>0.0493612</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.04628929302329</v>
+        <v>2.793090651525607</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08256539409469521</v>
+        <v>0.08254667261880164</v>
       </c>
       <c r="C26">
-        <v>22666.75566385488</v>
+        <v>22378.42577557357</v>
       </c>
       <c r="D26">
-        <v>28772.58361952823</v>
+        <v>28784.33822939997</v>
       </c>
       <c r="E26">
-        <v>4324.878140367736</v>
+        <v>4624.962638520792</v>
       </c>
       <c r="F26">
-        <v>7202.027955673346</v>
+        <v>7502.112453826402</v>
       </c>
       <c r="G26">
         <v>1096.2</v>
@@ -3425,28 +3425,28 @@
         <v>1162.7</v>
       </c>
       <c r="M26">
-        <v>416.2772158379194</v>
+        <v>433.6220998311661</v>
       </c>
       <c r="N26">
-        <v>746.4227841620809</v>
+        <v>729.0779001688343</v>
       </c>
       <c r="O26">
-        <v>108.9777264876638</v>
+        <v>106.4453734246498</v>
       </c>
       <c r="P26">
-        <v>637.4450576744171</v>
+        <v>622.6325267441845</v>
       </c>
       <c r="Q26">
-        <v>1597.545057674417</v>
+        <v>1582.732526744184</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09305092907196739</v>
+        <v>0.09360849682506886</v>
       </c>
       <c r="T26">
-        <v>1.091245475103173</v>
+        <v>1.104122328523531</v>
       </c>
       <c r="U26">
         <v>0.0578</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.793090651525608</v>
+        <v>2.681367025464583</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08254667261880164</v>
+        <v>0.08252795114290808</v>
       </c>
       <c r="C27">
-        <v>22378.42577557357</v>
+        <v>22090.10549555864</v>
       </c>
       <c r="D27">
-        <v>28784.33822939997</v>
+        <v>28796.1024475381</v>
       </c>
       <c r="E27">
-        <v>4624.962638520792</v>
+        <v>4925.047136673848</v>
       </c>
       <c r="F27">
-        <v>7502.112453826402</v>
+        <v>7802.196951979458</v>
       </c>
       <c r="G27">
         <v>1096.2</v>
@@ -3507,28 +3507,28 @@
         <v>1162.7</v>
       </c>
       <c r="M27">
-        <v>433.6220998311661</v>
+        <v>450.9669838244128</v>
       </c>
       <c r="N27">
-        <v>729.0779001688343</v>
+        <v>711.7330161755875</v>
       </c>
       <c r="O27">
-        <v>106.4453734246498</v>
+        <v>103.9130203616358</v>
       </c>
       <c r="P27">
-        <v>622.6325267441845</v>
+        <v>607.8199958139518</v>
       </c>
       <c r="Q27">
-        <v>1582.732526744184</v>
+        <v>1567.919995813952</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09360849682506886</v>
+        <v>0.09418113397690281</v>
       </c>
       <c r="T27">
-        <v>1.104122328523531</v>
+        <v>1.117347205009303</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.681367025464583</v>
+        <v>2.578237524485176</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08252795114290808</v>
+        <v>0.08331625966701453</v>
       </c>
       <c r="C28">
-        <v>22090.10549555864</v>
+        <v>21302.84447465186</v>
       </c>
       <c r="D28">
-        <v>28796.1024475381</v>
+        <v>28308.92592478437</v>
       </c>
       <c r="E28">
-        <v>4925.047136673848</v>
+        <v>5225.131634826905</v>
       </c>
       <c r="F28">
-        <v>7802.196951979458</v>
+        <v>8102.281450132515</v>
       </c>
       <c r="G28">
         <v>1096.2</v>
@@ -3589,45 +3589,45 @@
         <v>1162.7</v>
       </c>
       <c r="M28">
-        <v>450.9669838244128</v>
+        <v>496.6698528931232</v>
       </c>
       <c r="N28">
-        <v>711.7330161755875</v>
+        <v>666.0301471068772</v>
       </c>
       <c r="O28">
-        <v>103.9130203616358</v>
+        <v>97.24040147760407</v>
       </c>
       <c r="P28">
-        <v>607.8199958139518</v>
+        <v>568.7897456292731</v>
       </c>
       <c r="Q28">
-        <v>1567.919995813952</v>
+        <v>1528.889745629273</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09418113397690281</v>
+        <v>0.09476945981782813</v>
       </c>
       <c r="T28">
-        <v>1.117347205009303</v>
+        <v>1.130934406878248</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.146</v>
       </c>
       <c r="W28">
-        <v>0.0493612</v>
+        <v>0.0523502</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.578237524485176</v>
+        <v>2.340991693430199</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08331625966701453</v>
+        <v>0.08332742819112096</v>
       </c>
       <c r="C29">
-        <v>21302.84447465186</v>
+        <v>20995.9762002901</v>
       </c>
       <c r="D29">
-        <v>28308.92592478437</v>
+        <v>28302.14214857567</v>
       </c>
       <c r="E29">
-        <v>5225.131634826905</v>
+        <v>5525.216132979961</v>
       </c>
       <c r="F29">
-        <v>8102.281450132515</v>
+        <v>8402.365948285571</v>
       </c>
       <c r="G29">
         <v>1096.2</v>
@@ -3671,28 +3671,28 @@
         <v>1162.7</v>
       </c>
       <c r="M29">
-        <v>496.6698528931232</v>
+        <v>515.0650326299055</v>
       </c>
       <c r="N29">
-        <v>666.0301471068772</v>
+        <v>647.6349673700947</v>
       </c>
       <c r="O29">
-        <v>97.24040147760407</v>
+        <v>94.55470523603383</v>
       </c>
       <c r="P29">
-        <v>568.7897456292731</v>
+        <v>553.0802621340609</v>
       </c>
       <c r="Q29">
-        <v>1528.889745629273</v>
+        <v>1513.180262134061</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09476945981782813</v>
+        <v>0.09537412804322357</v>
       </c>
       <c r="T29">
-        <v>1.130934406878248</v>
+        <v>1.14489903102133</v>
       </c>
       <c r="U29">
         <v>0.0613</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.340991693430199</v>
+        <v>2.257384847236263</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08332742819112096</v>
+        <v>0.08403204471522741</v>
       </c>
       <c r="C30">
-        <v>20995.9762002901</v>
+        <v>20274.38180512428</v>
       </c>
       <c r="D30">
-        <v>28302.14214857567</v>
+        <v>27880.6322515629</v>
       </c>
       <c r="E30">
-        <v>5525.216132979961</v>
+        <v>5825.300631133018</v>
       </c>
       <c r="F30">
-        <v>8402.365948285571</v>
+        <v>8702.450446438628</v>
       </c>
       <c r="G30">
         <v>1096.2</v>
@@ -3753,45 +3753,45 @@
         <v>1162.7</v>
       </c>
       <c r="M30">
-        <v>515.0650326299055</v>
+        <v>557.8270736167161</v>
       </c>
       <c r="N30">
-        <v>647.6349673700947</v>
+        <v>604.8729263832842</v>
       </c>
       <c r="O30">
-        <v>94.55470523603383</v>
+        <v>88.31144725195948</v>
       </c>
       <c r="P30">
-        <v>553.0802621340609</v>
+        <v>516.5614791313246</v>
       </c>
       <c r="Q30">
-        <v>1513.180262134061</v>
+        <v>1476.661479131325</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09537412804322357</v>
+        <v>0.09599582917637661</v>
       </c>
       <c r="T30">
-        <v>1.14489903102133</v>
+        <v>1.159257024858583</v>
       </c>
       <c r="U30">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.146</v>
       </c>
       <c r="W30">
-        <v>0.0523502</v>
+        <v>0.0547414</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.257384847236263</v>
+        <v>2.084337700681221</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08403204471522739</v>
+        <v>0.08406712523933382</v>
       </c>
       <c r="C31">
-        <v>20274.38180512429</v>
+        <v>19953.63958476991</v>
       </c>
       <c r="D31">
-        <v>27880.63225156291</v>
+        <v>27859.97452936159</v>
       </c>
       <c r="E31">
-        <v>5825.300631133016</v>
+        <v>6125.385129286072</v>
       </c>
       <c r="F31">
-        <v>8702.450446438626</v>
+        <v>9002.534944591682</v>
       </c>
       <c r="G31">
         <v>1096.2</v>
@@ -3835,28 +3835,28 @@
         <v>1162.7</v>
       </c>
       <c r="M31">
-        <v>557.827073616716</v>
+        <v>577.0624899483269</v>
       </c>
       <c r="N31">
-        <v>604.8729263832843</v>
+        <v>585.6375100516734</v>
       </c>
       <c r="O31">
-        <v>88.31144725195949</v>
+        <v>85.50307646754432</v>
       </c>
       <c r="P31">
-        <v>516.5614791313247</v>
+        <v>500.1344335841291</v>
       </c>
       <c r="Q31">
-        <v>1476.661479131325</v>
+        <v>1460.234433584129</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09599582917637661</v>
+        <v>0.09663529319904833</v>
       </c>
       <c r="T31">
-        <v>1.159257024858583</v>
+        <v>1.174025247091186</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.084337700681221</v>
+        <v>2.014859777325181</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08406712523933382</v>
+        <v>0.08719966376344027</v>
       </c>
       <c r="C32">
-        <v>19953.63958476991</v>
+        <v>17924.6642098664</v>
       </c>
       <c r="D32">
-        <v>27859.97452936159</v>
+        <v>26131.08365261114</v>
       </c>
       <c r="E32">
-        <v>6125.385129286072</v>
+        <v>6425.469627439129</v>
       </c>
       <c r="F32">
-        <v>9002.534944591682</v>
+        <v>9302.619442744739</v>
       </c>
       <c r="G32">
         <v>1096.2</v>
@@ -3917,45 +3917,45 @@
         <v>1162.7</v>
       </c>
       <c r="M32">
-        <v>577.0624899483269</v>
+        <v>705.1385537600513</v>
       </c>
       <c r="N32">
-        <v>585.6375100516734</v>
+        <v>457.561446239949</v>
       </c>
       <c r="O32">
-        <v>85.50307646754432</v>
+        <v>66.80397115103254</v>
       </c>
       <c r="P32">
-        <v>500.1344335841291</v>
+        <v>390.7574750889164</v>
       </c>
       <c r="Q32">
-        <v>1460.234433584129</v>
+        <v>1350.857475088917</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09663529319904833</v>
+        <v>0.09729329241078299</v>
       </c>
       <c r="T32">
-        <v>1.174025247091186</v>
+        <v>1.189221533736328</v>
       </c>
       <c r="U32">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
         <v>0.146</v>
       </c>
       <c r="W32">
-        <v>0.0547414</v>
+        <v>0.0647332</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.014859777325181</v>
+        <v>1.64889580040698</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08719966376344027</v>
+        <v>0.0873346622875467</v>
       </c>
       <c r="C33">
-        <v>17924.6642098664</v>
+        <v>17554.88224723433</v>
       </c>
       <c r="D33">
-        <v>26131.08365261114</v>
+        <v>26061.38618813213</v>
       </c>
       <c r="E33">
-        <v>6425.469627439129</v>
+        <v>6725.554125592184</v>
       </c>
       <c r="F33">
-        <v>9302.619442744739</v>
+        <v>9602.703940897794</v>
       </c>
       <c r="G33">
         <v>1096.2</v>
@@ -3999,28 +3999,28 @@
         <v>1162.7</v>
       </c>
       <c r="M33">
-        <v>705.1385537600513</v>
+        <v>727.8849587200529</v>
       </c>
       <c r="N33">
-        <v>457.561446239949</v>
+        <v>434.8150412799474</v>
       </c>
       <c r="O33">
-        <v>66.80397115103254</v>
+        <v>63.48299602687232</v>
       </c>
       <c r="P33">
-        <v>390.7574750889164</v>
+        <v>371.3320452530751</v>
       </c>
       <c r="Q33">
-        <v>1350.857475088917</v>
+        <v>1331.432045253075</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09729329241078299</v>
+        <v>0.09797064454050985</v>
       </c>
       <c r="T33">
-        <v>1.189221533736328</v>
+        <v>1.204864769988681</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.64889580040698</v>
+        <v>1.597367806644262</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0873346622875467</v>
+        <v>0.08746966081165312</v>
       </c>
       <c r="C34">
-        <v>17554.88224723433</v>
+        <v>17185.47109313146</v>
       </c>
       <c r="D34">
-        <v>26061.38618813213</v>
+        <v>25992.05953218231</v>
       </c>
       <c r="E34">
-        <v>6725.554125592184</v>
+        <v>7025.638623745242</v>
       </c>
       <c r="F34">
-        <v>9602.703940897794</v>
+        <v>9902.788439050852</v>
       </c>
       <c r="G34">
         <v>1096.2</v>
@@ -4081,28 +4081,28 @@
         <v>1162.7</v>
       </c>
       <c r="M34">
-        <v>727.8849587200529</v>
+        <v>750.6313636800546</v>
       </c>
       <c r="N34">
-        <v>434.8150412799474</v>
+        <v>412.0686363199457</v>
       </c>
       <c r="O34">
-        <v>63.48299602687232</v>
+        <v>60.16202090271207</v>
       </c>
       <c r="P34">
-        <v>371.3320452530751</v>
+        <v>351.9066154172336</v>
       </c>
       <c r="Q34">
-        <v>1331.432045253075</v>
+        <v>1312.006615417234</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09797064454050985</v>
+        <v>0.09866821613679572</v>
       </c>
       <c r="T34">
-        <v>1.204864769988681</v>
+        <v>1.220974968517222</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.597367806644262</v>
+        <v>1.548962721594436</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08746966081165312</v>
+        <v>0.08760465933575956</v>
       </c>
       <c r="C35">
-        <v>17185.47109313146</v>
+        <v>16816.42779621287</v>
       </c>
       <c r="D35">
-        <v>25992.05953218231</v>
+        <v>25923.10073341677</v>
       </c>
       <c r="E35">
-        <v>7025.638623745242</v>
+        <v>7325.723121898297</v>
       </c>
       <c r="F35">
-        <v>9902.788439050852</v>
+        <v>10202.87293720391</v>
       </c>
       <c r="G35">
         <v>1096.2</v>
@@ -4163,28 +4163,28 @@
         <v>1162.7</v>
       </c>
       <c r="M35">
-        <v>750.6313636800546</v>
+        <v>773.3777686400562</v>
       </c>
       <c r="N35">
-        <v>412.0686363199457</v>
+        <v>389.3222313599441</v>
       </c>
       <c r="O35">
-        <v>60.16202090271207</v>
+        <v>56.84104577855184</v>
       </c>
       <c r="P35">
-        <v>351.9066154172336</v>
+        <v>332.4811855813923</v>
       </c>
       <c r="Q35">
-        <v>1312.006615417234</v>
+        <v>1292.581185581392</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09866821613679572</v>
+        <v>0.09938692626630238</v>
       </c>
       <c r="T35">
-        <v>1.220974968517222</v>
+        <v>1.237573354879963</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.548962721594436</v>
+        <v>1.503404994488717</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08760465933575956</v>
+        <v>0.1010627945406747</v>
       </c>
       <c r="C36">
-        <v>16816.42779621287</v>
+        <v>11094.12087272651</v>
       </c>
       <c r="D36">
-        <v>25923.10073341677</v>
+        <v>20500.87830808347</v>
       </c>
       <c r="E36">
-        <v>7325.723121898297</v>
+        <v>7625.807620051354</v>
       </c>
       <c r="F36">
-        <v>10202.87293720391</v>
+        <v>10502.95743535696</v>
       </c>
       <c r="G36">
         <v>1096.2</v>
@@ -4245,45 +4245,45 @@
         <v>1162.7</v>
       </c>
       <c r="M36">
-        <v>773.3777686400562</v>
+        <v>1245.650751833336</v>
       </c>
       <c r="N36">
-        <v>389.3222313599441</v>
+        <v>-82.95075183333574</v>
       </c>
       <c r="O36">
-        <v>56.84104577855184</v>
+        <v>-12.11080976766702</v>
       </c>
       <c r="P36">
-        <v>332.4811855813923</v>
+        <v>-70.83994206566872</v>
       </c>
       <c r="Q36">
-        <v>1292.581185581392</v>
+        <v>889.2600579343313</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09938692626630238</v>
+        <v>0.1003225762373806</v>
       </c>
       <c r="T36">
-        <v>1.237573354879963</v>
+        <v>1.259181899246665</v>
       </c>
       <c r="U36">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V36">
-        <v>0.146</v>
+        <v>0.1362775238164931</v>
       </c>
       <c r="W36">
-        <v>0.0647332</v>
+        <v>0.1024374856753639</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.503404994488717</v>
+        <v>0.9334076973732407</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1010627945406747</v>
+        <v>0.1017907945406747</v>
       </c>
       <c r="C37">
-        <v>11094.12087272651</v>
+        <v>10564.67351719699</v>
       </c>
       <c r="D37">
-        <v>20500.87830808347</v>
+        <v>20271.51545070701</v>
       </c>
       <c r="E37">
-        <v>7625.807620051354</v>
+        <v>7925.89211820441</v>
       </c>
       <c r="F37">
-        <v>10502.95743535696</v>
+        <v>10803.04193351002</v>
       </c>
       <c r="G37">
         <v>1096.2</v>
@@ -4327,37 +4327,37 @@
         <v>1162.7</v>
       </c>
       <c r="M37">
-        <v>1245.650751833336</v>
+        <v>1281.240773314288</v>
       </c>
       <c r="N37">
-        <v>-82.95075183333574</v>
+        <v>-118.5407733142881</v>
       </c>
       <c r="O37">
-        <v>-12.11080976766702</v>
+        <v>-17.30695290388606</v>
       </c>
       <c r="P37">
-        <v>-70.83994206566872</v>
+        <v>-101.233820410402</v>
       </c>
       <c r="Q37">
-        <v>889.2600579343313</v>
+        <v>858.866179589598</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1003225762373806</v>
+        <v>0.1011744914910897</v>
       </c>
       <c r="T37">
-        <v>1.259181899246665</v>
+        <v>1.278856616422394</v>
       </c>
       <c r="U37">
         <v>0.1186</v>
       </c>
       <c r="V37">
-        <v>0.1362775238164931</v>
+        <v>0.1324920370438128</v>
       </c>
       <c r="W37">
-        <v>0.1024374856753639</v>
+        <v>0.1028864444066038</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.9334076973732407</v>
+        <v>0.9074797057795396</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1017907945406747</v>
+        <v>0.1025187945406748</v>
       </c>
       <c r="C38">
-        <v>10564.67351719699</v>
+        <v>10040.30157974139</v>
       </c>
       <c r="D38">
-        <v>20271.51545070701</v>
+        <v>20047.22801140446</v>
       </c>
       <c r="E38">
-        <v>7925.892118204408</v>
+        <v>8225.976616357464</v>
       </c>
       <c r="F38">
-        <v>10803.04193351002</v>
+        <v>11103.12643166307</v>
       </c>
       <c r="G38">
         <v>1096.2</v>
@@ -4409,37 +4409,37 @@
         <v>1162.7</v>
       </c>
       <c r="M38">
-        <v>1281.240773314288</v>
+        <v>1316.830794795241</v>
       </c>
       <c r="N38">
-        <v>-118.5407733142879</v>
+        <v>-154.1307947952405</v>
       </c>
       <c r="O38">
-        <v>-17.30695290388603</v>
+        <v>-22.50309604010511</v>
       </c>
       <c r="P38">
-        <v>-101.2338204104019</v>
+        <v>-131.6276987551354</v>
       </c>
       <c r="Q38">
-        <v>858.8661795895981</v>
+        <v>828.4723012448646</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1011744914910897</v>
+        <v>0.1020534516734879</v>
       </c>
       <c r="T38">
-        <v>1.278856616422394</v>
+        <v>1.299155927794178</v>
       </c>
       <c r="U38">
         <v>0.1186</v>
       </c>
       <c r="V38">
-        <v>0.1324920370438128</v>
+        <v>0.1289111711777638</v>
       </c>
       <c r="W38">
-        <v>0.1028864444066038</v>
+        <v>0.1033111350983172</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.9074797057795398</v>
+        <v>0.8829532272449575</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1025187945406748</v>
+        <v>0.1032467945406748</v>
       </c>
       <c r="C39">
-        <v>10040.30157974139</v>
+        <v>9520.838438071814</v>
       </c>
       <c r="D39">
-        <v>20047.22801140446</v>
+        <v>19827.84936788795</v>
       </c>
       <c r="E39">
-        <v>8225.976616357464</v>
+        <v>8526.061114510521</v>
       </c>
       <c r="F39">
-        <v>11103.12643166307</v>
+        <v>11403.21092981613</v>
       </c>
       <c r="G39">
         <v>1096.2</v>
@@ -4491,37 +4491,37 @@
         <v>1162.7</v>
       </c>
       <c r="M39">
-        <v>1316.830794795241</v>
+        <v>1352.420816276193</v>
       </c>
       <c r="N39">
-        <v>-154.1307947952405</v>
+        <v>-189.7208162761931</v>
       </c>
       <c r="O39">
-        <v>-22.50309604010511</v>
+        <v>-27.69923917632419</v>
       </c>
       <c r="P39">
-        <v>-131.6276987551354</v>
+        <v>-162.0215770998689</v>
       </c>
       <c r="Q39">
-        <v>828.4723012448646</v>
+        <v>798.0784229001312</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1020534516734879</v>
+        <v>0.1029607654101571</v>
       </c>
       <c r="T39">
-        <v>1.299155927794178</v>
+        <v>1.320110055661826</v>
       </c>
       <c r="U39">
         <v>0.1186</v>
       </c>
       <c r="V39">
-        <v>0.1289111711777638</v>
+        <v>0.1255187719362437</v>
       </c>
       <c r="W39">
-        <v>0.1033111350983172</v>
+        <v>0.1037134736483615</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8829532272449575</v>
+        <v>0.8597176160016691</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1032467945406748</v>
+        <v>0.1039747945406748</v>
       </c>
       <c r="C40">
-        <v>9520.838438071814</v>
+        <v>9006.124684402967</v>
       </c>
       <c r="D40">
-        <v>19827.84936788795</v>
+        <v>19613.22011237215</v>
       </c>
       <c r="E40">
-        <v>8526.061114510521</v>
+        <v>8826.145612663579</v>
       </c>
       <c r="F40">
-        <v>11403.21092981613</v>
+        <v>11703.29542796919</v>
       </c>
       <c r="G40">
         <v>1096.2</v>
@@ -4573,37 +4573,37 @@
         <v>1162.7</v>
       </c>
       <c r="M40">
-        <v>1352.420816276193</v>
+        <v>1388.010837757146</v>
       </c>
       <c r="N40">
-        <v>-189.7208162761931</v>
+        <v>-225.3108377571455</v>
       </c>
       <c r="O40">
-        <v>-27.69923917632419</v>
+        <v>-32.89538231254323</v>
       </c>
       <c r="P40">
-        <v>-162.0215770998689</v>
+        <v>-192.4154554446022</v>
       </c>
       <c r="Q40">
-        <v>798.0784229001312</v>
+        <v>767.6845445553978</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1029607654101571</v>
+        <v>0.1038978271381924</v>
       </c>
       <c r="T40">
-        <v>1.320110055661826</v>
+        <v>1.341751204115299</v>
       </c>
       <c r="U40">
         <v>0.1186</v>
       </c>
       <c r="V40">
-        <v>0.1255187719362437</v>
+        <v>0.1223003418865964</v>
       </c>
       <c r="W40">
-        <v>0.1037134736483615</v>
+        <v>0.1040951794522497</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8597176160016691</v>
+        <v>0.8376735745657289</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1039747945406748</v>
+        <v>0.1047027945406748</v>
       </c>
       <c r="C41">
-        <v>9006.124684402967</v>
+        <v>8496.007739161741</v>
       </c>
       <c r="D41">
-        <v>19613.22011237215</v>
+        <v>19403.18766528399</v>
       </c>
       <c r="E41">
-        <v>8826.145612663579</v>
+        <v>9126.230110816636</v>
       </c>
       <c r="F41">
-        <v>11703.29542796919</v>
+        <v>12003.37992612224</v>
       </c>
       <c r="G41">
         <v>1096.2</v>
@@ -4655,37 +4655,37 @@
         <v>1162.7</v>
       </c>
       <c r="M41">
-        <v>1388.010837757146</v>
+        <v>1423.600859238098</v>
       </c>
       <c r="N41">
-        <v>-225.3108377571455</v>
+        <v>-260.9008592380981</v>
       </c>
       <c r="O41">
-        <v>-32.89538231254323</v>
+        <v>-38.09152544876231</v>
       </c>
       <c r="P41">
-        <v>-192.4154554446022</v>
+        <v>-222.8093337893358</v>
       </c>
       <c r="Q41">
-        <v>767.6845445553978</v>
+        <v>737.2906662106643</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1038978271381924</v>
+        <v>0.1048661242571623</v>
       </c>
       <c r="T41">
-        <v>1.341751204115299</v>
+        <v>1.364113724183887</v>
       </c>
       <c r="U41">
         <v>0.1186</v>
       </c>
       <c r="V41">
-        <v>0.1223003418865964</v>
+        <v>0.1192428333394315</v>
       </c>
       <c r="W41">
-        <v>0.1040951794522497</v>
+        <v>0.1044577999659434</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8376735745657289</v>
+        <v>0.8167317352015856</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1047027945406748</v>
+        <v>0.1398594273786405</v>
       </c>
       <c r="C42">
-        <v>8496.007739161741</v>
+        <v>1582.002002214618</v>
       </c>
       <c r="D42">
-        <v>19403.18766528399</v>
+        <v>12789.26642648992</v>
       </c>
       <c r="E42">
-        <v>9126.230110816636</v>
+        <v>9426.314608969689</v>
       </c>
       <c r="F42">
-        <v>12003.37992612224</v>
+        <v>12303.4644242753</v>
       </c>
       <c r="G42">
         <v>1096.2</v>
@@ -4737,45 +4737,45 @@
         <v>1162.7</v>
       </c>
       <c r="M42">
-        <v>1423.600859238098</v>
+        <v>2470.53565639448</v>
       </c>
       <c r="N42">
-        <v>-260.9008592380981</v>
+        <v>-1307.83565639448</v>
       </c>
       <c r="O42">
-        <v>-38.09152544876231</v>
+        <v>-190.944005833594</v>
       </c>
       <c r="P42">
-        <v>-222.8093337893358</v>
+        <v>-1116.891650560886</v>
       </c>
       <c r="Q42">
-        <v>737.2906662106643</v>
+        <v>-156.7916505608858</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1048661242571623</v>
+        <v>0.1070988260885816</v>
       </c>
       <c r="T42">
-        <v>1.364113724183887</v>
+        <v>1.415677276872555</v>
       </c>
       <c r="U42">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1192428333394315</v>
+        <v>0.06871149564695646</v>
       </c>
       <c r="W42">
-        <v>0.1044577999659434</v>
+        <v>0.1870027316740911</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.8167317352015856</v>
+        <v>0.4706266825134005</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1398594273786405</v>
+        <v>0.1414094273786405</v>
       </c>
       <c r="C43">
-        <v>1582.002002214618</v>
+        <v>1092.562042588333</v>
       </c>
       <c r="D43">
-        <v>12789.26642648992</v>
+        <v>12599.91096501669</v>
       </c>
       <c r="E43">
-        <v>9426.314608969689</v>
+        <v>9726.399107122746</v>
       </c>
       <c r="F43">
-        <v>12303.4644242753</v>
+        <v>12603.54892242836</v>
       </c>
       <c r="G43">
         <v>1096.2</v>
@@ -4819,37 +4819,37 @@
         <v>1162.7</v>
       </c>
       <c r="M43">
-        <v>2470.53565639448</v>
+        <v>2530.792623623614</v>
       </c>
       <c r="N43">
-        <v>-1307.83565639448</v>
+        <v>-1368.092623623614</v>
       </c>
       <c r="O43">
-        <v>-190.944005833594</v>
+        <v>-199.7415230490477</v>
       </c>
       <c r="P43">
-        <v>-1116.891650560886</v>
+        <v>-1168.351100574567</v>
       </c>
       <c r="Q43">
-        <v>-156.7916505608858</v>
+        <v>-208.2511005745665</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1070988260885816</v>
+        <v>0.1081557024004537</v>
       </c>
       <c r="T43">
-        <v>1.415677276872555</v>
+        <v>1.440085505784151</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.06871149564695646</v>
+        <v>0.06707550765536223</v>
       </c>
       <c r="W43">
-        <v>0.1870027316740911</v>
+        <v>0.1873312380628033</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4706266825134005</v>
+        <v>0.4594212853107003</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1414094273786405</v>
+        <v>0.1429594273786405</v>
       </c>
       <c r="C44">
-        <v>1092.562042588335</v>
+        <v>608.6473985308785</v>
       </c>
       <c r="D44">
-        <v>12599.91096501669</v>
+        <v>12416.08081911229</v>
       </c>
       <c r="E44">
-        <v>9726.399107122746</v>
+        <v>10026.4836052758</v>
       </c>
       <c r="F44">
-        <v>12603.54892242836</v>
+        <v>12903.63342058141</v>
       </c>
       <c r="G44">
         <v>1096.2</v>
@@ -4901,37 +4901,37 @@
         <v>1162.7</v>
       </c>
       <c r="M44">
-        <v>2530.792623623614</v>
+        <v>2591.049590852747</v>
       </c>
       <c r="N44">
-        <v>-1368.092623623614</v>
+        <v>-1428.349590852747</v>
       </c>
       <c r="O44">
-        <v>-199.7415230490476</v>
+        <v>-208.5390402645011</v>
       </c>
       <c r="P44">
-        <v>-1168.351100574566</v>
+        <v>-1219.810550588246</v>
       </c>
       <c r="Q44">
-        <v>-208.2511005745661</v>
+        <v>-259.7105505882458</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1081557024004537</v>
+        <v>0.1092496620916898</v>
       </c>
       <c r="T44">
-        <v>1.440085505784151</v>
+        <v>1.465350163780364</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.06707550765536224</v>
+        <v>0.06551561212849337</v>
       </c>
       <c r="W44">
-        <v>0.1873312380628033</v>
+        <v>0.1876444650845985</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4594212853107004</v>
+        <v>0.4487370693732423</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1429594273786405</v>
+        <v>0.1445094273786405</v>
       </c>
       <c r="C45">
-        <v>608.6473985308785</v>
+        <v>130.0197079950867</v>
       </c>
       <c r="D45">
-        <v>12416.08081911229</v>
+        <v>12237.53762672955</v>
       </c>
       <c r="E45">
-        <v>10026.4836052758</v>
+        <v>10326.56810342886</v>
       </c>
       <c r="F45">
-        <v>12903.63342058141</v>
+        <v>13203.71791873447</v>
       </c>
       <c r="G45">
         <v>1096.2</v>
@@ -4983,37 +4983,37 @@
         <v>1162.7</v>
       </c>
       <c r="M45">
-        <v>2591.049590852747</v>
+        <v>2651.306558081881</v>
       </c>
       <c r="N45">
-        <v>-1428.349590852747</v>
+        <v>-1488.606558081881</v>
       </c>
       <c r="O45">
-        <v>-208.5390402645011</v>
+        <v>-217.3365574799546</v>
       </c>
       <c r="P45">
-        <v>-1219.810550588246</v>
+        <v>-1271.270000601926</v>
       </c>
       <c r="Q45">
-        <v>-259.7105505882458</v>
+        <v>-311.1700006019263</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1092496620916898</v>
+        <v>0.1103826917718985</v>
       </c>
       <c r="T45">
-        <v>1.465350163780364</v>
+        <v>1.491517130990728</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.06551561212849337</v>
+        <v>0.06402662094375489</v>
       </c>
       <c r="W45">
-        <v>0.1876444650845985</v>
+        <v>0.187943454514494</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4487370693732423</v>
+        <v>0.4385384996147594</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1445094273786405</v>
+        <v>0.1460594273786406</v>
       </c>
       <c r="C46">
-        <v>130.0197079950867</v>
+        <v>-343.5458748482288</v>
       </c>
       <c r="D46">
-        <v>12237.53762672955</v>
+        <v>12064.05654203929</v>
       </c>
       <c r="E46">
-        <v>10326.56810342886</v>
+        <v>10626.65260158191</v>
       </c>
       <c r="F46">
-        <v>13203.71791873447</v>
+        <v>13503.80241688752</v>
       </c>
       <c r="G46">
         <v>1096.2</v>
@@ -5065,37 +5065,37 @@
         <v>1162.7</v>
       </c>
       <c r="M46">
-        <v>2651.306558081881</v>
+        <v>2711.563525311015</v>
       </c>
       <c r="N46">
-        <v>-1488.606558081881</v>
+        <v>-1548.863525311015</v>
       </c>
       <c r="O46">
-        <v>-217.3365574799546</v>
+        <v>-226.1340746954081</v>
       </c>
       <c r="P46">
-        <v>-1271.270000601926</v>
+        <v>-1322.729450615607</v>
       </c>
       <c r="Q46">
-        <v>-311.1700006019263</v>
+        <v>-362.6294506156065</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1103826917718985</v>
+        <v>0.1115569225313876</v>
       </c>
       <c r="T46">
-        <v>1.491517130990728</v>
+        <v>1.518635624281468</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.06402662094375489</v>
+        <v>0.06260380714500477</v>
       </c>
       <c r="W46">
-        <v>0.187943454514494</v>
+        <v>0.188229155525283</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4385384996147594</v>
+        <v>0.4287931996233203</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1460594273786406</v>
+        <v>0.1476094273786406</v>
       </c>
       <c r="C47">
-        <v>-343.5458748482288</v>
+        <v>-812.2616242580298</v>
       </c>
       <c r="D47">
-        <v>12064.05654203929</v>
+        <v>11895.42529078255</v>
       </c>
       <c r="E47">
-        <v>10626.65260158191</v>
+        <v>10926.73709973497</v>
       </c>
       <c r="F47">
-        <v>13503.80241688752</v>
+        <v>13803.88691504058</v>
       </c>
       <c r="G47">
         <v>1096.2</v>
@@ -5147,37 +5147,37 @@
         <v>1162.7</v>
       </c>
       <c r="M47">
-        <v>2711.563525311015</v>
+        <v>2771.820492540149</v>
       </c>
       <c r="N47">
-        <v>-1548.863525311015</v>
+        <v>-1609.120492540148</v>
       </c>
       <c r="O47">
-        <v>-226.1340746954081</v>
+        <v>-234.9315919108617</v>
       </c>
       <c r="P47">
-        <v>-1322.729450615607</v>
+        <v>-1374.188900629287</v>
       </c>
       <c r="Q47">
-        <v>-362.6294506156065</v>
+        <v>-414.0889006292867</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1115569225313876</v>
+        <v>0.1127746433190059</v>
       </c>
       <c r="T47">
-        <v>1.518635624281468</v>
+        <v>1.546758506212607</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.06260380714500477</v>
+        <v>0.06124285481576553</v>
       </c>
       <c r="W47">
-        <v>0.188229155525283</v>
+        <v>0.1885024347529943</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4287931996233203</v>
+        <v>0.4194716083271612</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1476094273786406</v>
+        <v>0.1491594273786405</v>
       </c>
       <c r="C48">
-        <v>-812.2616242580298</v>
+        <v>-1276.32810943728</v>
       </c>
       <c r="D48">
-        <v>11895.42529078255</v>
+        <v>11731.44330375636</v>
       </c>
       <c r="E48">
-        <v>10926.73709973497</v>
+        <v>11226.82159788803</v>
       </c>
       <c r="F48">
-        <v>13803.88691504058</v>
+        <v>14103.97141319364</v>
       </c>
       <c r="G48">
         <v>1096.2</v>
@@ -5229,37 +5229,37 @@
         <v>1162.7</v>
       </c>
       <c r="M48">
-        <v>2771.820492540149</v>
+        <v>2832.077459769282</v>
       </c>
       <c r="N48">
-        <v>-1609.120492540148</v>
+        <v>-1669.377459769282</v>
       </c>
       <c r="O48">
-        <v>-234.9315919108617</v>
+        <v>-243.7291091263151</v>
       </c>
       <c r="P48">
-        <v>-1374.188900629287</v>
+        <v>-1425.648350642967</v>
       </c>
       <c r="Q48">
-        <v>-414.0889006292867</v>
+        <v>-465.5483506429667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1127746433190059</v>
+        <v>0.1140383158344588</v>
       </c>
       <c r="T48">
-        <v>1.546758506212607</v>
+        <v>1.575942628971335</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.06124285481576553</v>
+        <v>0.0599398153516003</v>
       </c>
       <c r="W48">
-        <v>0.1885024347529943</v>
+        <v>0.1887640850773987</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4194716083271612</v>
+        <v>0.4105466804904131</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1491594273786405</v>
+        <v>0.1507094273786405</v>
       </c>
       <c r="C49">
-        <v>-1276.32810943728</v>
+        <v>-1735.934990350819</v>
       </c>
       <c r="D49">
-        <v>11731.44330375636</v>
+        <v>11571.92092099587</v>
       </c>
       <c r="E49">
-        <v>11226.82159788803</v>
+        <v>11526.90609604108</v>
       </c>
       <c r="F49">
-        <v>14103.97141319364</v>
+        <v>14404.05591134669</v>
       </c>
       <c r="G49">
         <v>1096.2</v>
@@ -5311,37 +5311,37 @@
         <v>1162.7</v>
       </c>
       <c r="M49">
-        <v>2832.077459769282</v>
+        <v>2892.334426998416</v>
       </c>
       <c r="N49">
-        <v>-1669.377459769282</v>
+        <v>-1729.634426998416</v>
       </c>
       <c r="O49">
-        <v>-243.7291091263151</v>
+        <v>-252.5266263417687</v>
       </c>
       <c r="P49">
-        <v>-1425.648350642967</v>
+        <v>-1477.107800656647</v>
       </c>
       <c r="Q49">
-        <v>-465.5483506429667</v>
+        <v>-517.0078006566474</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1140383158344588</v>
+        <v>0.1153505911389676</v>
       </c>
       <c r="T49">
-        <v>1.575942628971335</v>
+        <v>1.606249217990015</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.0599398153516003</v>
+        <v>0.05869106919844196</v>
       </c>
       <c r="W49">
-        <v>0.1887640850773987</v>
+        <v>0.1890148333049529</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4105466804904131</v>
+        <v>0.4019936246468627</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1507094273786405</v>
+        <v>0.1522594273786405</v>
       </c>
       <c r="C50">
-        <v>-1735.934990350814</v>
+        <v>-2191.261749485773</v>
       </c>
       <c r="D50">
-        <v>11571.92092099588</v>
+        <v>11416.67866001397</v>
       </c>
       <c r="E50">
-        <v>11526.90609604108</v>
+        <v>11826.99059419414</v>
       </c>
       <c r="F50">
-        <v>14404.05591134669</v>
+        <v>14704.14040949975</v>
       </c>
       <c r="G50">
         <v>1096.2</v>
@@ -5393,37 +5393,37 @@
         <v>1162.7</v>
       </c>
       <c r="M50">
-        <v>2892.334426998416</v>
+        <v>2952.591394227549</v>
       </c>
       <c r="N50">
-        <v>-1729.634426998416</v>
+        <v>-1789.891394227549</v>
       </c>
       <c r="O50">
-        <v>-252.5266263417687</v>
+        <v>-261.3241435572222</v>
       </c>
       <c r="P50">
-        <v>-1477.107800656647</v>
+        <v>-1528.567250670327</v>
       </c>
       <c r="Q50">
-        <v>-517.007800656647</v>
+        <v>-568.4672506703267</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1153505911389676</v>
+        <v>0.1167143282201238</v>
       </c>
       <c r="T50">
-        <v>1.606249217990015</v>
+        <v>1.637744300695701</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.05869106919844197</v>
+        <v>0.05749329227602479</v>
       </c>
       <c r="W50">
-        <v>0.1890148333049529</v>
+        <v>0.1892553469109742</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4019936246468628</v>
+        <v>0.3937896731234575</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1522594273786405</v>
+        <v>0.1538094273786405</v>
       </c>
       <c r="C51">
-        <v>-2191.261749485773</v>
+        <v>-2642.4783654905</v>
       </c>
       <c r="D51">
-        <v>11416.67866001397</v>
+        <v>11265.5465421623</v>
       </c>
       <c r="E51">
-        <v>11826.99059419414</v>
+        <v>12127.07509234719</v>
       </c>
       <c r="F51">
-        <v>14704.14040949975</v>
+        <v>15004.2249076528</v>
       </c>
       <c r="G51">
         <v>1096.2</v>
@@ -5475,37 +5475,37 @@
         <v>1162.7</v>
       </c>
       <c r="M51">
-        <v>2952.591394227549</v>
+        <v>3012.848361456683</v>
       </c>
       <c r="N51">
-        <v>-1789.891394227549</v>
+        <v>-1850.148361456683</v>
       </c>
       <c r="O51">
-        <v>-261.3241435572222</v>
+        <v>-270.1216607726757</v>
       </c>
       <c r="P51">
-        <v>-1528.567250670327</v>
+        <v>-1580.026700684007</v>
       </c>
       <c r="Q51">
-        <v>-568.4672506703267</v>
+        <v>-619.9267006840072</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1167143282201238</v>
+        <v>0.1181326147845263</v>
       </c>
       <c r="T51">
-        <v>1.637744300695701</v>
+        <v>1.670499186709615</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.05749329227602479</v>
+        <v>0.05634342643050429</v>
       </c>
       <c r="W51">
-        <v>0.1892553469109742</v>
+        <v>0.1894862399727547</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3937896731234575</v>
+        <v>0.3859138796609883</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1538094273786405</v>
+        <v>0.1553594273786405</v>
       </c>
       <c r="C52">
-        <v>-2642.4783654905</v>
+        <v>-3089.745934007344</v>
       </c>
       <c r="D52">
-        <v>11265.5465421623</v>
+        <v>11118.36347179852</v>
       </c>
       <c r="E52">
-        <v>12127.07509234719</v>
+        <v>12427.15959050025</v>
       </c>
       <c r="F52">
-        <v>15004.2249076528</v>
+        <v>15304.30940580586</v>
       </c>
       <c r="G52">
         <v>1096.2</v>
@@ -5557,37 +5557,37 @@
         <v>1162.7</v>
       </c>
       <c r="M52">
-        <v>3012.848361456683</v>
+        <v>3073.105328685817</v>
       </c>
       <c r="N52">
-        <v>-1850.148361456683</v>
+        <v>-1910.405328685817</v>
       </c>
       <c r="O52">
-        <v>-270.1216607726757</v>
+        <v>-278.9191779881292</v>
       </c>
       <c r="P52">
-        <v>-1580.026700684007</v>
+        <v>-1631.486150697687</v>
       </c>
       <c r="Q52">
-        <v>-619.9267006840072</v>
+        <v>-671.3861506976874</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1181326147845263</v>
+        <v>0.1196087905964554</v>
       </c>
       <c r="T52">
-        <v>1.670499186709615</v>
+        <v>1.704591006846546</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.05634342643050429</v>
+        <v>0.0552386533632395</v>
       </c>
       <c r="W52">
-        <v>0.1894862399727547</v>
+        <v>0.1897080784046615</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3859138796609883</v>
+        <v>0.3783469408441061</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1553594273786405</v>
+        <v>0.1569094273786406</v>
       </c>
       <c r="C53">
-        <v>-3089.745934007344</v>
+        <v>-3533.217240466431</v>
       </c>
       <c r="D53">
-        <v>11118.36347179852</v>
+        <v>10974.97666349249</v>
       </c>
       <c r="E53">
-        <v>12427.15959050025</v>
+        <v>12727.24408865331</v>
       </c>
       <c r="F53">
-        <v>15304.30940580586</v>
+        <v>15604.39390395892</v>
       </c>
       <c r="G53">
         <v>1096.2</v>
@@ -5639,37 +5639,37 @@
         <v>1162.7</v>
       </c>
       <c r="M53">
-        <v>3073.105328685817</v>
+        <v>3133.362295914951</v>
       </c>
       <c r="N53">
-        <v>-1910.405328685817</v>
+        <v>-1970.66229591495</v>
       </c>
       <c r="O53">
-        <v>-278.9191779881292</v>
+        <v>-287.7166952035827</v>
       </c>
       <c r="P53">
-        <v>-1631.486150697687</v>
+        <v>-1682.945600711368</v>
       </c>
       <c r="Q53">
-        <v>-671.3861506976874</v>
+        <v>-722.8456007113676</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1196087905964554</v>
+        <v>0.1211464737338816</v>
       </c>
       <c r="T53">
-        <v>1.704591006846546</v>
+        <v>1.740103319489183</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.0552386533632395</v>
+        <v>0.05417637156779258</v>
       </c>
       <c r="W53">
-        <v>0.1897080784046615</v>
+        <v>0.1899213845891873</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3783469408441061</v>
+        <v>0.3710710381355656</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1569094273786406</v>
+        <v>0.1584594273786405</v>
       </c>
       <c r="C54">
-        <v>-3533.217240466431</v>
+        <v>-3973.037289121925</v>
       </c>
       <c r="D54">
-        <v>10974.97666349249</v>
+        <v>10835.24111299005</v>
       </c>
       <c r="E54">
-        <v>12727.24408865331</v>
+        <v>13027.32858680636</v>
       </c>
       <c r="F54">
-        <v>15604.39390395892</v>
+        <v>15904.47840211197</v>
       </c>
       <c r="G54">
         <v>1096.2</v>
@@ -5721,37 +5721,37 @@
         <v>1162.7</v>
       </c>
       <c r="M54">
-        <v>3133.362295914951</v>
+        <v>3193.619263144084</v>
       </c>
       <c r="N54">
-        <v>-1970.66229591495</v>
+        <v>-2030.919263144084</v>
       </c>
       <c r="O54">
-        <v>-287.7166952035827</v>
+        <v>-296.5142124190363</v>
       </c>
       <c r="P54">
-        <v>-1682.945600711368</v>
+        <v>-1734.405050725048</v>
       </c>
       <c r="Q54">
-        <v>-722.8456007113676</v>
+        <v>-774.3050507250479</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1211464737338816</v>
+        <v>0.1227495901963046</v>
       </c>
       <c r="T54">
-        <v>1.740103319489183</v>
+        <v>1.777126794371931</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.05417637156779258</v>
+        <v>0.05315417587783423</v>
       </c>
       <c r="W54">
-        <v>0.1899213845891873</v>
+        <v>0.1901266414837309</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3710710381355656</v>
+        <v>0.3640696977933852</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1584594273786405</v>
+        <v>0.1600094273786405</v>
       </c>
       <c r="C55">
-        <v>-3973.037289121925</v>
+        <v>-4409.343792181584</v>
       </c>
       <c r="D55">
-        <v>10835.24111299005</v>
+        <v>10699.01910808344</v>
       </c>
       <c r="E55">
-        <v>13027.32858680636</v>
+        <v>13327.41308495942</v>
       </c>
       <c r="F55">
-        <v>15904.47840211197</v>
+        <v>16204.56290026503</v>
       </c>
       <c r="G55">
         <v>1096.2</v>
@@ -5803,37 +5803,37 @@
         <v>1162.7</v>
       </c>
       <c r="M55">
-        <v>3193.619263144084</v>
+        <v>3253.876230373218</v>
       </c>
       <c r="N55">
-        <v>-2030.919263144084</v>
+        <v>-2091.176230373218</v>
       </c>
       <c r="O55">
-        <v>-296.5142124190363</v>
+        <v>-305.3117296344897</v>
       </c>
       <c r="P55">
-        <v>-1734.405050725048</v>
+        <v>-1785.864500738728</v>
       </c>
       <c r="Q55">
-        <v>-774.3050507250479</v>
+        <v>-825.7645007387279</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1227495901963046</v>
+        <v>0.1244224073744851</v>
       </c>
       <c r="T55">
-        <v>1.777126794371931</v>
+        <v>1.81575998555393</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.05315417587783423</v>
+        <v>0.05216983928750397</v>
       </c>
       <c r="W55">
-        <v>0.1901266414837309</v>
+        <v>0.1903242962710692</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3640696977933852</v>
+        <v>0.3573276663527669</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1600094273786405</v>
+        <v>0.1615594273786405</v>
       </c>
       <c r="C56">
-        <v>-4409.343792181584</v>
+        <v>-4842.267622498075</v>
       </c>
       <c r="D56">
-        <v>10699.01910808344</v>
+        <v>10566.17977592001</v>
       </c>
       <c r="E56">
-        <v>13327.41308495942</v>
+        <v>13627.49758311248</v>
       </c>
       <c r="F56">
-        <v>16204.56290026503</v>
+        <v>16504.64739841808</v>
       </c>
       <c r="G56">
         <v>1096.2</v>
@@ -5885,37 +5885,37 @@
         <v>1162.7</v>
       </c>
       <c r="M56">
-        <v>3253.876230373218</v>
+        <v>3314.133197602352</v>
       </c>
       <c r="N56">
-        <v>-2091.176230373218</v>
+        <v>-2151.433197602351</v>
       </c>
       <c r="O56">
-        <v>-305.3117296344897</v>
+        <v>-314.1092468499433</v>
       </c>
       <c r="P56">
-        <v>-1785.864500738728</v>
+        <v>-1837.323950752408</v>
       </c>
       <c r="Q56">
-        <v>-825.7645007387279</v>
+        <v>-877.2239507524081</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1244224073744851</v>
+        <v>0.126169571982807</v>
       </c>
       <c r="T56">
-        <v>1.81575998555393</v>
+        <v>1.856110207455128</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.05216983928750397</v>
+        <v>0.05122129675500389</v>
       </c>
       <c r="W56">
-        <v>0.1903242962710692</v>
+        <v>0.1905147636115952</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3573276663527669</v>
+        <v>0.3508307996918075</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1615594273786405</v>
+        <v>0.1631094273786405</v>
       </c>
       <c r="C57">
-        <v>-4842.267622498075</v>
+        <v>-5271.933232950088</v>
       </c>
       <c r="D57">
-        <v>10566.17977592001</v>
+        <v>10436.59866362105</v>
       </c>
       <c r="E57">
-        <v>13627.49758311248</v>
+        <v>13927.58208126553</v>
       </c>
       <c r="F57">
-        <v>16504.64739841808</v>
+        <v>16804.73189657114</v>
       </c>
       <c r="G57">
         <v>1096.2</v>
@@ -5967,37 +5967,37 @@
         <v>1162.7</v>
       </c>
       <c r="M57">
-        <v>3314.133197602352</v>
+        <v>3374.390164831485</v>
       </c>
       <c r="N57">
-        <v>-2151.433197602351</v>
+        <v>-2211.690164831485</v>
       </c>
       <c r="O57">
-        <v>-314.1092468499433</v>
+        <v>-322.9067640653968</v>
       </c>
       <c r="P57">
-        <v>-1837.323950752408</v>
+        <v>-1888.783400766088</v>
       </c>
       <c r="Q57">
-        <v>-877.2239507524081</v>
+        <v>-928.6834007660883</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.126169571982807</v>
+        <v>0.1279961531642345</v>
       </c>
       <c r="T57">
-        <v>1.856110207455128</v>
+        <v>1.898294530351836</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.05122129675500389</v>
+        <v>0.05030663074152168</v>
       </c>
       <c r="W57">
-        <v>0.1905147636115952</v>
+        <v>0.1906984285471024</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3508307996918075</v>
+        <v>0.3445659639830253</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1631094273786405</v>
+        <v>0.1646594273786405</v>
       </c>
       <c r="C58">
-        <v>-5271.933232950088</v>
+        <v>-5698.459045338155</v>
       </c>
       <c r="D58">
-        <v>10436.59866362105</v>
+        <v>10310.15734938604</v>
       </c>
       <c r="E58">
-        <v>13927.58208126553</v>
+        <v>14227.66657941859</v>
       </c>
       <c r="F58">
-        <v>16804.73189657114</v>
+        <v>17104.8163947242</v>
       </c>
       <c r="G58">
         <v>1096.2</v>
@@ -6049,37 +6049,37 @@
         <v>1162.7</v>
       </c>
       <c r="M58">
-        <v>3374.390164831485</v>
+        <v>3434.647132060619</v>
       </c>
       <c r="N58">
-        <v>-2211.690164831485</v>
+        <v>-2271.947132060619</v>
       </c>
       <c r="O58">
-        <v>-322.9067640653968</v>
+        <v>-331.7042812808504</v>
       </c>
       <c r="P58">
-        <v>-1888.783400766088</v>
+        <v>-1940.242850779769</v>
       </c>
       <c r="Q58">
-        <v>-928.6834007660883</v>
+        <v>-980.1428507797685</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1279961531642345</v>
+        <v>0.1299076916099143</v>
       </c>
       <c r="T58">
-        <v>1.898294530351836</v>
+        <v>1.942440914778623</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.05030663074152168</v>
+        <v>0.04942405827237218</v>
       </c>
       <c r="W58">
-        <v>0.1906984285471024</v>
+        <v>0.1908756490989077</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3445659639830253</v>
+        <v>0.3385209470710423</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1646594273786405</v>
+        <v>0.1662094273786406</v>
       </c>
       <c r="C59">
-        <v>-5698.459045338155</v>
+        <v>-6121.957811349614</v>
       </c>
       <c r="D59">
-        <v>10310.15734938604</v>
+        <v>10186.74308152764</v>
       </c>
       <c r="E59">
-        <v>14227.66657941859</v>
+        <v>14527.75107757165</v>
       </c>
       <c r="F59">
-        <v>17104.8163947242</v>
+        <v>17404.90089287726</v>
       </c>
       <c r="G59">
         <v>1096.2</v>
@@ -6131,37 +6131,37 @@
         <v>1162.7</v>
       </c>
       <c r="M59">
-        <v>3434.647132060619</v>
+        <v>3494.904099289753</v>
       </c>
       <c r="N59">
-        <v>-2271.947132060619</v>
+        <v>-2332.204099289753</v>
       </c>
       <c r="O59">
-        <v>-331.7042812808504</v>
+        <v>-340.5017984963039</v>
       </c>
       <c r="P59">
-        <v>-1940.242850779769</v>
+        <v>-1991.702300793449</v>
       </c>
       <c r="Q59">
-        <v>-980.1428507797685</v>
+        <v>-1031.602300793449</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1299076916099143</v>
+        <v>0.1319102556958647</v>
       </c>
       <c r="T59">
-        <v>1.942440914778623</v>
+        <v>1.988689507987637</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.04942405827237218</v>
+        <v>0.04857191933664162</v>
       </c>
       <c r="W59">
-        <v>0.1908756490989077</v>
+        <v>0.1910467585972024</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3385209470710423</v>
+        <v>0.3326843790180933</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1662094273786405</v>
+        <v>0.1677594273786405</v>
       </c>
       <c r="C60">
-        <v>-6121.95781134961</v>
+        <v>-6542.536947905341</v>
       </c>
       <c r="D60">
-        <v>10186.74308152764</v>
+        <v>10066.24844312496</v>
       </c>
       <c r="E60">
-        <v>14527.75107757164</v>
+        <v>14827.8355757247</v>
       </c>
       <c r="F60">
-        <v>17404.90089287725</v>
+        <v>17704.98539103031</v>
       </c>
       <c r="G60">
         <v>1096.2</v>
@@ -6213,37 +6213,37 @@
         <v>1162.7</v>
       </c>
       <c r="M60">
-        <v>3494.904099289753</v>
+        <v>3555.161066518885</v>
       </c>
       <c r="N60">
-        <v>-2332.204099289752</v>
+        <v>-2392.461066518885</v>
       </c>
       <c r="O60">
-        <v>-340.5017984963038</v>
+        <v>-349.2993157117572</v>
       </c>
       <c r="P60">
-        <v>-1991.702300793449</v>
+        <v>-2043.161750807128</v>
       </c>
       <c r="Q60">
-        <v>-1031.602300793449</v>
+        <v>-1083.061750807128</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1319102556958646</v>
+        <v>0.1340105058347882</v>
       </c>
       <c r="T60">
-        <v>1.988689507987637</v>
+        <v>2.037194130133677</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.04857191933664163</v>
+        <v>0.04774866646652907</v>
       </c>
       <c r="W60">
-        <v>0.1910467585972024</v>
+        <v>0.191212067773521</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3326843790180933</v>
+        <v>0.3270456607296511</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1677594273786405</v>
+        <v>0.1693094273786405</v>
       </c>
       <c r="C61">
-        <v>-6542.536947905341</v>
+        <v>-6960.29884898475</v>
       </c>
       <c r="D61">
-        <v>10066.24844312496</v>
+        <v>9948.571040198613</v>
       </c>
       <c r="E61">
-        <v>14827.8355757247</v>
+        <v>15127.92007387775</v>
       </c>
       <c r="F61">
-        <v>17704.98539103031</v>
+        <v>18005.06988918336</v>
       </c>
       <c r="G61">
         <v>1096.2</v>
@@ -6295,37 +6295,37 @@
         <v>1162.7</v>
       </c>
       <c r="M61">
-        <v>3555.161066518885</v>
+        <v>3615.418033748019</v>
       </c>
       <c r="N61">
-        <v>-2392.461066518885</v>
+        <v>-2452.718033748019</v>
       </c>
       <c r="O61">
-        <v>-349.2993157117572</v>
+        <v>-358.0968329272108</v>
       </c>
       <c r="P61">
-        <v>-2043.161750807128</v>
+        <v>-2094.621200820808</v>
       </c>
       <c r="Q61">
-        <v>-1083.061750807128</v>
+        <v>-1134.521200820808</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1340105058347882</v>
+        <v>0.1362157684806579</v>
       </c>
       <c r="T61">
-        <v>2.037194130133677</v>
+        <v>2.088123983387019</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.04774866646652907</v>
+        <v>0.04695285535875358</v>
       </c>
       <c r="W61">
-        <v>0.191212067773521</v>
+        <v>0.1913718666439623</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3270456607296511</v>
+        <v>0.3215948997174903</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1693094273786405</v>
+        <v>0.1708594273786405</v>
       </c>
       <c r="C62">
-        <v>-6960.29884898475</v>
+        <v>-7375.341175831423</v>
       </c>
       <c r="D62">
-        <v>9948.571040198613</v>
+        <v>9833.613211504997</v>
       </c>
       <c r="E62">
-        <v>15127.92007387775</v>
+        <v>15428.00457203081</v>
       </c>
       <c r="F62">
-        <v>18005.06988918336</v>
+        <v>18305.15438733642</v>
       </c>
       <c r="G62">
         <v>1096.2</v>
@@ -6377,37 +6377,37 @@
         <v>1162.7</v>
       </c>
       <c r="M62">
-        <v>3615.418033748019</v>
+        <v>3675.675000977154</v>
       </c>
       <c r="N62">
-        <v>-2452.718033748019</v>
+        <v>-2512.975000977153</v>
       </c>
       <c r="O62">
-        <v>-358.0968329272108</v>
+        <v>-366.8943501426643</v>
       </c>
       <c r="P62">
-        <v>-2094.621200820808</v>
+        <v>-2146.080650834489</v>
       </c>
       <c r="Q62">
-        <v>-1134.521200820808</v>
+        <v>-1185.980650834489</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1362157684806579</v>
+        <v>0.1385341215186235</v>
       </c>
       <c r="T62">
-        <v>2.088123983387019</v>
+        <v>2.141665623986686</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.04695285535875358</v>
+        <v>0.04618313641844615</v>
       </c>
       <c r="W62">
-        <v>0.1913718666439623</v>
+        <v>0.191526426207176</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3215948997174903</v>
+        <v>0.316322852181138</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1708594273786405</v>
+        <v>0.1724094273786405</v>
       </c>
       <c r="C63">
-        <v>-7375.341175831423</v>
+        <v>-7787.757127268413</v>
       </c>
       <c r="D63">
-        <v>9833.613211504997</v>
+        <v>9721.281758221065</v>
       </c>
       <c r="E63">
-        <v>15428.00457203081</v>
+        <v>15728.08907018387</v>
       </c>
       <c r="F63">
-        <v>18305.15438733642</v>
+        <v>18605.23888548948</v>
       </c>
       <c r="G63">
         <v>1096.2</v>
@@ -6459,37 +6459,37 @@
         <v>1162.7</v>
       </c>
       <c r="M63">
-        <v>3675.675000977154</v>
+        <v>3735.931968206287</v>
       </c>
       <c r="N63">
-        <v>-2512.975000977153</v>
+        <v>-2573.231968206287</v>
       </c>
       <c r="O63">
-        <v>-366.8943501426643</v>
+        <v>-375.6918673581179</v>
       </c>
       <c r="P63">
-        <v>-2146.080650834489</v>
+        <v>-2197.540100848169</v>
       </c>
       <c r="Q63">
-        <v>-1185.980650834489</v>
+        <v>-1237.440100848169</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1385341215186235</v>
+        <v>0.1409744931375346</v>
       </c>
       <c r="T63">
-        <v>2.141665623986686</v>
+        <v>2.198025245670546</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.04618313641844615</v>
+        <v>0.04543824712137443</v>
       </c>
       <c r="W63">
-        <v>0.191526426207176</v>
+        <v>0.191675999978028</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.316322852181138</v>
+        <v>0.3112208706943455</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1724094273786405</v>
+        <v>0.1739594273786405</v>
       </c>
       <c r="C64">
-        <v>-7787.757127268413</v>
+        <v>-8197.635691695488</v>
       </c>
       <c r="D64">
-        <v>9721.281758221065</v>
+        <v>9611.487691947046</v>
       </c>
       <c r="E64">
-        <v>15728.08907018387</v>
+        <v>16028.17356833693</v>
       </c>
       <c r="F64">
-        <v>18605.23888548948</v>
+        <v>18905.32338364254</v>
       </c>
       <c r="G64">
         <v>1096.2</v>
@@ -6541,37 +6541,37 @@
         <v>1162.7</v>
       </c>
       <c r="M64">
-        <v>3735.931968206287</v>
+        <v>3796.188935435421</v>
       </c>
       <c r="N64">
-        <v>-2573.231968206287</v>
+        <v>-2633.488935435421</v>
       </c>
       <c r="O64">
-        <v>-375.6918673581179</v>
+        <v>-384.4893845735714</v>
       </c>
       <c r="P64">
-        <v>-2197.540100848169</v>
+        <v>-2248.999550861849</v>
       </c>
       <c r="Q64">
-        <v>-1237.440100848169</v>
+        <v>-1288.89955086185</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1409744931375346</v>
+        <v>0.1435467767358464</v>
       </c>
       <c r="T64">
-        <v>2.198025245670546</v>
+        <v>2.257431333391372</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.04543824712137443</v>
+        <v>0.04471700510357483</v>
       </c>
       <c r="W64">
-        <v>0.191675999978028</v>
+        <v>0.1918208253752022</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3112208706943455</v>
+        <v>0.3062808568738002</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1739594273786405</v>
+        <v>0.1755094273786405</v>
       </c>
       <c r="C65">
-        <v>-8197.635691695488</v>
+        <v>-8605.061882200484</v>
       </c>
       <c r="D65">
-        <v>9611.487691947046</v>
+        <v>9504.145999595105</v>
       </c>
       <c r="E65">
-        <v>16028.17356833693</v>
+        <v>16328.25806648998</v>
       </c>
       <c r="F65">
-        <v>18905.32338364254</v>
+        <v>19205.40788179559</v>
       </c>
       <c r="G65">
         <v>1096.2</v>
@@ -6623,37 +6623,37 @@
         <v>1162.7</v>
       </c>
       <c r="M65">
-        <v>3796.188935435421</v>
+        <v>3856.445902664555</v>
       </c>
       <c r="N65">
-        <v>-2633.488935435421</v>
+        <v>-2693.745902664554</v>
       </c>
       <c r="O65">
-        <v>-384.4893845735714</v>
+        <v>-393.2869017890249</v>
       </c>
       <c r="P65">
-        <v>-2248.999550861849</v>
+        <v>-2300.459000875529</v>
       </c>
       <c r="Q65">
-        <v>-1288.89955086185</v>
+        <v>-1340.35900087553</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1435467767358464</v>
+        <v>0.1462619649785088</v>
       </c>
       <c r="T65">
-        <v>2.257431333391372</v>
+        <v>2.32013775931891</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.04471700510357483</v>
+        <v>0.04401830189883147</v>
       </c>
       <c r="W65">
-        <v>0.1918208253752022</v>
+        <v>0.1919611249787146</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3062808568738002</v>
+        <v>0.3014952184851472</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1755094273786405</v>
+        <v>0.1770594273786406</v>
       </c>
       <c r="C66">
-        <v>-8605.061882200484</v>
+        <v>-9010.116956090224</v>
       </c>
       <c r="D66">
-        <v>9504.145999595105</v>
+        <v>9399.175423858422</v>
       </c>
       <c r="E66">
-        <v>16328.25806648998</v>
+        <v>16628.34256464304</v>
       </c>
       <c r="F66">
-        <v>19205.40788179559</v>
+        <v>19505.49237994865</v>
       </c>
       <c r="G66">
         <v>1096.2</v>
@@ -6705,37 +6705,37 @@
         <v>1162.7</v>
       </c>
       <c r="M66">
-        <v>3856.445902664555</v>
+        <v>3916.702869893688</v>
       </c>
       <c r="N66">
-        <v>-2693.745902664554</v>
+        <v>-2754.002869893688</v>
       </c>
       <c r="O66">
-        <v>-393.2869017890249</v>
+        <v>-402.0844190044784</v>
       </c>
       <c r="P66">
-        <v>-2300.459000875529</v>
+        <v>-2351.918450889209</v>
       </c>
       <c r="Q66">
-        <v>-1340.35900087553</v>
+        <v>-1391.81845088921</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1462619649785088</v>
+        <v>0.1491323068350376</v>
       </c>
       <c r="T66">
-        <v>2.32013775931891</v>
+        <v>2.386427409585165</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.04401830189883147</v>
+        <v>0.04334109725423407</v>
       </c>
       <c r="W66">
-        <v>0.1919611249787146</v>
+        <v>0.1920971076713498</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3014952184851472</v>
+        <v>0.2968568305084526</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1770594273786406</v>
+        <v>0.1786094273786405</v>
       </c>
       <c r="C67">
-        <v>-9010.116956090224</v>
+        <v>-9412.878620032418</v>
       </c>
       <c r="D67">
-        <v>9399.175423858422</v>
+        <v>9296.498258069285</v>
       </c>
       <c r="E67">
-        <v>16628.34256464304</v>
+        <v>16928.42706279609</v>
       </c>
       <c r="F67">
-        <v>19505.49237994865</v>
+        <v>19805.5768781017</v>
       </c>
       <c r="G67">
         <v>1096.2</v>
@@ -6787,37 +6787,37 @@
         <v>1162.7</v>
       </c>
       <c r="M67">
-        <v>3916.702869893688</v>
+        <v>3976.959837122822</v>
       </c>
       <c r="N67">
-        <v>-2754.002869893688</v>
+        <v>-2814.259837122822</v>
       </c>
       <c r="O67">
-        <v>-402.0844190044784</v>
+        <v>-410.881936219932</v>
       </c>
       <c r="P67">
-        <v>-2351.918450889209</v>
+        <v>-2403.37790090289</v>
       </c>
       <c r="Q67">
-        <v>-1391.81845088921</v>
+        <v>-1443.27790090289</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1491323068350376</v>
+        <v>0.1521714923301858</v>
       </c>
       <c r="T67">
-        <v>2.386427409585165</v>
+        <v>2.456616451043552</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.04334109725423407</v>
+        <v>0.04268441396250324</v>
       </c>
       <c r="W67">
-        <v>0.1920971076713498</v>
+        <v>0.1922289696763294</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2968568305084526</v>
+        <v>0.2923589997431729</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1786094273786405</v>
+        <v>0.1801594273786405</v>
       </c>
       <c r="C68">
-        <v>-9412.878620032418</v>
+        <v>-9813.421221896977</v>
       </c>
       <c r="D68">
-        <v>9296.498258069285</v>
+        <v>9196.040154357783</v>
       </c>
       <c r="E68">
-        <v>16928.42706279609</v>
+        <v>17228.51156094915</v>
       </c>
       <c r="F68">
-        <v>19805.5768781017</v>
+        <v>20105.66137625476</v>
       </c>
       <c r="G68">
         <v>1096.2</v>
@@ -6869,37 +6869,37 @@
         <v>1162.7</v>
       </c>
       <c r="M68">
-        <v>3976.959837122822</v>
+        <v>4037.216804351956</v>
       </c>
       <c r="N68">
-        <v>-2814.259837122822</v>
+        <v>-2874.516804351956</v>
       </c>
       <c r="O68">
-        <v>-410.881936219932</v>
+        <v>-419.6794534353855</v>
       </c>
       <c r="P68">
-        <v>-2403.37790090289</v>
+        <v>-2454.83735091657</v>
       </c>
       <c r="Q68">
-        <v>-1443.27790090289</v>
+        <v>-1494.73735091657</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1521714923301858</v>
+        <v>0.155394870885646</v>
       </c>
       <c r="T68">
-        <v>2.456616451043552</v>
+        <v>2.531059373802448</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.04268441396250324</v>
+        <v>0.04204733315709275</v>
       </c>
       <c r="W68">
-        <v>0.1922289696763294</v>
+        <v>0.1923568955020558</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2923589997431729</v>
+        <v>0.2879954325828271</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1801594273786405</v>
+        <v>0.1817094273786405</v>
       </c>
       <c r="C69">
-        <v>-9813.421221896977</v>
+        <v>-10211.81593029204</v>
       </c>
       <c r="D69">
-        <v>9196.040154357783</v>
+        <v>9097.729944115777</v>
       </c>
       <c r="E69">
-        <v>17228.51156094915</v>
+        <v>17528.5960591022</v>
       </c>
       <c r="F69">
-        <v>20105.66137625476</v>
+        <v>20405.74587440781</v>
       </c>
       <c r="G69">
         <v>1096.2</v>
@@ -6951,37 +6951,37 @@
         <v>1162.7</v>
       </c>
       <c r="M69">
-        <v>4037.216804351956</v>
+        <v>4097.473771581089</v>
       </c>
       <c r="N69">
-        <v>-2874.516804351956</v>
+        <v>-2934.773771581089</v>
       </c>
       <c r="O69">
-        <v>-419.6794534353855</v>
+        <v>-428.4769706508389</v>
       </c>
       <c r="P69">
-        <v>-2454.83735091657</v>
+        <v>-2506.296800930249</v>
       </c>
       <c r="Q69">
-        <v>-1494.73735091657</v>
+        <v>-1546.19680093025</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.155394870885646</v>
+        <v>0.1588197106008224</v>
       </c>
       <c r="T69">
-        <v>2.531059373802448</v>
+        <v>2.610154979233774</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.04204733315709275</v>
+        <v>0.04142899002242963</v>
       </c>
       <c r="W69">
-        <v>0.1923568955020558</v>
+        <v>0.1924810588034961</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2879954325828271</v>
+        <v>0.2837602056330797</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1817094273786405</v>
+        <v>0.1832594273786405</v>
       </c>
       <c r="C70">
-        <v>-10211.81593029204</v>
+        <v>-10608.13090270584</v>
       </c>
       <c r="D70">
-        <v>9097.729944115777</v>
+        <v>9001.499469855027</v>
       </c>
       <c r="E70">
-        <v>17528.5960591022</v>
+        <v>17828.68055725526</v>
       </c>
       <c r="F70">
-        <v>20405.74587440781</v>
+        <v>20705.83037256087</v>
       </c>
       <c r="G70">
         <v>1096.2</v>
@@ -7033,37 +7033,37 @@
         <v>1162.7</v>
       </c>
       <c r="M70">
-        <v>4097.473771581089</v>
+        <v>4157.730738810223</v>
       </c>
       <c r="N70">
-        <v>-2934.773771581089</v>
+        <v>-2995.030738810222</v>
       </c>
       <c r="O70">
-        <v>-428.4769706508389</v>
+        <v>-437.2744878662924</v>
       </c>
       <c r="P70">
-        <v>-2506.296800930249</v>
+        <v>-2557.75625094393</v>
       </c>
       <c r="Q70">
-        <v>-1546.19680093025</v>
+        <v>-1597.65625094393</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1588197106008224</v>
+        <v>0.162465507716978</v>
       </c>
       <c r="T70">
-        <v>2.610154979233774</v>
+        <v>2.694353526950993</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.04142899002242963</v>
+        <v>0.04082856987717703</v>
       </c>
       <c r="W70">
-        <v>0.1924810588034961</v>
+        <v>0.1926016231686629</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2837602056330797</v>
+        <v>0.2796477388847741</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1832594273786405</v>
+        <v>0.1848094273786405</v>
       </c>
       <c r="C71">
-        <v>-10608.13090270584</v>
+        <v>-11002.43144308926</v>
       </c>
       <c r="D71">
-        <v>9001.499469855027</v>
+        <v>8907.283427624669</v>
       </c>
       <c r="E71">
-        <v>17828.68055725526</v>
+        <v>18128.76505540832</v>
       </c>
       <c r="F71">
-        <v>20705.83037256087</v>
+        <v>21005.91487071393</v>
       </c>
       <c r="G71">
         <v>1096.2</v>
@@ -7115,37 +7115,37 @@
         <v>1162.7</v>
       </c>
       <c r="M71">
-        <v>4157.730738810223</v>
+        <v>4217.987706039357</v>
       </c>
       <c r="N71">
-        <v>-2995.030738810222</v>
+        <v>-3055.287706039357</v>
       </c>
       <c r="O71">
-        <v>-437.2744878662924</v>
+        <v>-446.0720050817461</v>
       </c>
       <c r="P71">
-        <v>-2557.75625094393</v>
+        <v>-2609.215700957611</v>
       </c>
       <c r="Q71">
-        <v>-1597.65625094393</v>
+        <v>-1649.115700957611</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.162465507716978</v>
+        <v>0.1663543579742106</v>
       </c>
       <c r="T71">
-        <v>2.694353526950993</v>
+        <v>2.784165311182692</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.04082856987717703</v>
+        <v>0.04024530459321735</v>
       </c>
       <c r="W71">
-        <v>0.1926016231686629</v>
+        <v>0.192718742837682</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2796477388847741</v>
+        <v>0.2756527711864202</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1848094273786405</v>
+        <v>0.1863594273786406</v>
       </c>
       <c r="C72">
-        <v>-11002.43144308926</v>
+        <v>-11394.7801496446</v>
       </c>
       <c r="D72">
-        <v>8907.283427624669</v>
+        <v>8815.019219222389</v>
       </c>
       <c r="E72">
-        <v>18128.76505540832</v>
+        <v>18428.84955356138</v>
       </c>
       <c r="F72">
-        <v>21005.91487071393</v>
+        <v>21305.99936886699</v>
       </c>
       <c r="G72">
         <v>1096.2</v>
@@ -7197,37 +7197,37 @@
         <v>1162.7</v>
       </c>
       <c r="M72">
-        <v>4217.987706039357</v>
+        <v>4278.244673268491</v>
       </c>
       <c r="N72">
-        <v>-3055.287706039357</v>
+        <v>-3115.544673268491</v>
       </c>
       <c r="O72">
-        <v>-446.0720050817461</v>
+        <v>-454.8695222971996</v>
       </c>
       <c r="P72">
-        <v>-2609.215700957611</v>
+        <v>-2660.675150971291</v>
       </c>
       <c r="Q72">
-        <v>-1649.115700957611</v>
+        <v>-1700.575150971291</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1663543579742106</v>
+        <v>0.1705114048009075</v>
       </c>
       <c r="T72">
-        <v>2.784165311182692</v>
+        <v>2.880171011568303</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.04024530459321735</v>
+        <v>0.03967846931725653</v>
       </c>
       <c r="W72">
-        <v>0.192718742837682</v>
+        <v>0.1928325633610949</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2756527711864202</v>
+        <v>0.2717703377894283</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1863594273786405</v>
+        <v>0.1879094273786406</v>
       </c>
       <c r="C73">
-        <v>-11394.78014964459</v>
+        <v>-11785.23705352353</v>
       </c>
       <c r="D73">
-        <v>8815.019219222389</v>
+        <v>8724.646813496507</v>
       </c>
       <c r="E73">
-        <v>18428.84955356137</v>
+        <v>18728.93405171443</v>
       </c>
       <c r="F73">
-        <v>21305.99936886698</v>
+        <v>21606.08386702004</v>
       </c>
       <c r="G73">
         <v>1096.2</v>
@@ -7279,37 +7279,37 @@
         <v>1162.7</v>
       </c>
       <c r="M73">
-        <v>4278.24467326849</v>
+        <v>4338.501640497623</v>
       </c>
       <c r="N73">
-        <v>-3115.54467326849</v>
+        <v>-3175.801640497623</v>
       </c>
       <c r="O73">
-        <v>-454.8695222971995</v>
+        <v>-463.6670395126529</v>
       </c>
       <c r="P73">
-        <v>-2660.67515097129</v>
+        <v>-2712.13460098497</v>
       </c>
       <c r="Q73">
-        <v>-1700.57515097129</v>
+        <v>-1752.03460098497</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1705114048009074</v>
+        <v>0.174965383543797</v>
       </c>
       <c r="T73">
-        <v>2.880171011568302</v>
+        <v>2.983034261981456</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.03967846931725654</v>
+        <v>0.03912737946562798</v>
       </c>
       <c r="W73">
-        <v>0.1928325633610949</v>
+        <v>0.1929432222033019</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2717703377894284</v>
+        <v>0.2679957497645753</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1879094273786406</v>
+        <v>0.1894594273786405</v>
       </c>
       <c r="C74">
-        <v>-11785.23705352353</v>
+        <v>-12173.85974907999</v>
       </c>
       <c r="D74">
-        <v>8724.646813496507</v>
+        <v>8636.108616093099</v>
       </c>
       <c r="E74">
-        <v>18728.93405171443</v>
+        <v>19029.01854986748</v>
       </c>
       <c r="F74">
-        <v>21606.08386702004</v>
+        <v>21906.16836517309</v>
       </c>
       <c r="G74">
         <v>1096.2</v>
@@ -7361,37 +7361,37 @@
         <v>1162.7</v>
       </c>
       <c r="M74">
-        <v>4338.501640497623</v>
+        <v>4398.758607726757</v>
       </c>
       <c r="N74">
-        <v>-3175.801640497623</v>
+        <v>-3236.058607726757</v>
       </c>
       <c r="O74">
-        <v>-463.6670395126529</v>
+        <v>-472.4645567281065</v>
       </c>
       <c r="P74">
-        <v>-2712.13460098497</v>
+        <v>-2763.59405099865</v>
       </c>
       <c r="Q74">
-        <v>-1752.03460098497</v>
+        <v>-1803.49405099865</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.174965383543797</v>
+        <v>0.1797492866380117</v>
       </c>
       <c r="T74">
-        <v>2.983034261981456</v>
+        <v>3.093517012425213</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.03912737946562798</v>
+        <v>0.03859138796609884</v>
       </c>
       <c r="W74">
-        <v>0.1929432222033019</v>
+        <v>0.1930508492964074</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2679957497645753</v>
+        <v>0.264324575110266</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1894594273786405</v>
+        <v>0.1910094273786405</v>
       </c>
       <c r="C75">
-        <v>-12173.85974907999</v>
+        <v>-12560.70351627179</v>
       </c>
       <c r="D75">
-        <v>8636.108616093099</v>
+        <v>8549.349347054356</v>
       </c>
       <c r="E75">
-        <v>19029.01854986748</v>
+        <v>19329.10304802054</v>
       </c>
       <c r="F75">
-        <v>21906.16836517309</v>
+        <v>22206.25286332615</v>
       </c>
       <c r="G75">
         <v>1096.2</v>
@@ -7443,37 +7443,37 @@
         <v>1162.7</v>
       </c>
       <c r="M75">
-        <v>4398.758607726757</v>
+        <v>4459.015574955891</v>
       </c>
       <c r="N75">
-        <v>-3236.058607726757</v>
+        <v>-3296.31557495589</v>
       </c>
       <c r="O75">
-        <v>-472.4645567281065</v>
+        <v>-481.26207394356</v>
       </c>
       <c r="P75">
-        <v>-2763.59405099865</v>
+        <v>-2815.05350101233</v>
       </c>
       <c r="Q75">
-        <v>-1803.49405099865</v>
+        <v>-1854.95350101233</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1797492866380117</v>
+        <v>0.1849011822779352</v>
       </c>
       <c r="T75">
-        <v>3.093517012425213</v>
+        <v>3.212498435980029</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.03859138796609884</v>
+        <v>0.03806988272331371</v>
       </c>
       <c r="W75">
-        <v>0.1930508492964074</v>
+        <v>0.1931555675491586</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.264324575110266</v>
+        <v>0.2607526213925597</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1910094273786405</v>
+        <v>0.1925594273786405</v>
       </c>
       <c r="C76">
-        <v>-12560.70351627179</v>
+        <v>-12945.82143575772</v>
       </c>
       <c r="D76">
-        <v>8549.349347054356</v>
+        <v>8464.31592572149</v>
       </c>
       <c r="E76">
-        <v>19329.10304802054</v>
+        <v>19629.1875461736</v>
       </c>
       <c r="F76">
-        <v>22206.25286332615</v>
+        <v>22506.33736147921</v>
       </c>
       <c r="G76">
         <v>1096.2</v>
@@ -7525,37 +7525,37 @@
         <v>1162.7</v>
       </c>
       <c r="M76">
-        <v>4459.015574955891</v>
+        <v>4519.272542185025</v>
       </c>
       <c r="N76">
-        <v>-3296.31557495589</v>
+        <v>-3356.572542185024</v>
       </c>
       <c r="O76">
-        <v>-481.26207394356</v>
+        <v>-490.0595911590135</v>
       </c>
       <c r="P76">
-        <v>-2815.05350101233</v>
+        <v>-2866.512951026011</v>
       </c>
       <c r="Q76">
-        <v>-1854.95350101233</v>
+        <v>-1906.412951026011</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1849011822779352</v>
+        <v>0.1904652295690527</v>
       </c>
       <c r="T76">
-        <v>3.212498435980029</v>
+        <v>3.340998373419231</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.03806988272331371</v>
+        <v>0.03756228428700286</v>
       </c>
       <c r="W76">
-        <v>0.1931555675491586</v>
+        <v>0.1932574933151698</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2607526213925597</v>
+        <v>0.2572759197739922</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1925594273786405</v>
+        <v>0.1941094273786405</v>
       </c>
       <c r="C77">
-        <v>-12945.82143575772</v>
+        <v>-13329.26449719355</v>
       </c>
       <c r="D77">
-        <v>8464.31592572149</v>
+        <v>8380.95736243871</v>
       </c>
       <c r="E77">
-        <v>19629.1875461736</v>
+        <v>19929.27204432666</v>
       </c>
       <c r="F77">
-        <v>22506.33736147921</v>
+        <v>22806.42185963226</v>
       </c>
       <c r="G77">
         <v>1096.2</v>
@@ -7607,37 +7607,37 @@
         <v>1162.7</v>
       </c>
       <c r="M77">
-        <v>4519.272542185025</v>
+        <v>4579.529509414158</v>
       </c>
       <c r="N77">
-        <v>-3356.572542185024</v>
+        <v>-3416.829509414158</v>
       </c>
       <c r="O77">
-        <v>-490.0595911590135</v>
+        <v>-498.857108374467</v>
       </c>
       <c r="P77">
-        <v>-2866.512951026011</v>
+        <v>-2917.972401039691</v>
       </c>
       <c r="Q77">
-        <v>-1906.412951026011</v>
+        <v>-1957.872401039691</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1904652295690527</v>
+        <v>0.1964929474677632</v>
       </c>
       <c r="T77">
-        <v>3.340998373419231</v>
+        <v>3.480206638978365</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.03756228428700286</v>
+        <v>0.03706804370427914</v>
       </c>
       <c r="W77">
-        <v>0.1932574933151698</v>
+        <v>0.1933567368241808</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2572759197739922</v>
+        <v>0.2538907103032818</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1941094273786405</v>
+        <v>0.1956594273786406</v>
       </c>
       <c r="C78">
-        <v>-13329.26449719355</v>
+        <v>-13711.08170119143</v>
       </c>
       <c r="D78">
-        <v>8380.95736243871</v>
+        <v>8299.224656593884</v>
       </c>
       <c r="E78">
-        <v>19929.27204432666</v>
+        <v>20229.35654247971</v>
       </c>
       <c r="F78">
-        <v>22806.42185963226</v>
+        <v>23106.50635778532</v>
       </c>
       <c r="G78">
         <v>1096.2</v>
@@ -7689,37 +7689,37 @@
         <v>1162.7</v>
       </c>
       <c r="M78">
-        <v>4579.529509414158</v>
+        <v>4639.786476643292</v>
       </c>
       <c r="N78">
-        <v>-3416.829509414158</v>
+        <v>-3477.086476643292</v>
       </c>
       <c r="O78">
-        <v>-498.857108374467</v>
+        <v>-507.6546255899206</v>
       </c>
       <c r="P78">
-        <v>-2917.972401039691</v>
+        <v>-2969.431851053371</v>
       </c>
       <c r="Q78">
-        <v>-1957.872401039691</v>
+        <v>-2009.331851053371</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1964929474677632</v>
+        <v>0.2030448147489703</v>
       </c>
       <c r="T78">
-        <v>3.480206638978365</v>
+        <v>3.631519971107859</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.03706804370427914</v>
+        <v>0.0365866405392885</v>
       </c>
       <c r="W78">
-        <v>0.1933567368241808</v>
+        <v>0.1934534025797109</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2538907103032818</v>
+        <v>0.2505934283512911</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1956594273786406</v>
+        <v>0.1972094273786406</v>
       </c>
       <c r="C79">
-        <v>-13711.08170119143</v>
+        <v>-14091.32015537081</v>
       </c>
       <c r="D79">
-        <v>8299.224656593884</v>
+        <v>8219.070700567567</v>
       </c>
       <c r="E79">
-        <v>20229.35654247971</v>
+        <v>20529.44104063277</v>
       </c>
       <c r="F79">
-        <v>23106.50635778532</v>
+        <v>23406.59085593838</v>
       </c>
       <c r="G79">
         <v>1096.2</v>
@@ -7771,37 +7771,37 @@
         <v>1162.7</v>
       </c>
       <c r="M79">
-        <v>4639.786476643292</v>
+        <v>4700.043443872426</v>
       </c>
       <c r="N79">
-        <v>-3477.086476643292</v>
+        <v>-3537.343443872426</v>
       </c>
       <c r="O79">
-        <v>-507.6546255899206</v>
+        <v>-516.4521428053741</v>
       </c>
       <c r="P79">
-        <v>-2969.431851053371</v>
+        <v>-3020.891301067052</v>
       </c>
       <c r="Q79">
-        <v>-2009.331851053371</v>
+        <v>-2060.791301067052</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2030448147489703</v>
+        <v>0.2101923063284689</v>
       </c>
       <c r="T79">
-        <v>3.631519971107859</v>
+        <v>3.796589060703671</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.0365866405392885</v>
+        <v>0.03611758104519506</v>
       </c>
       <c r="W79">
-        <v>0.1934534025797109</v>
+        <v>0.1935475897261248</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2505934283512911</v>
+        <v>0.2473806920903772</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1972094273786406</v>
+        <v>0.1987594273786406</v>
       </c>
       <c r="C80">
-        <v>-14091.32015537081</v>
+        <v>-14470.02516489666</v>
       </c>
       <c r="D80">
-        <v>8219.070700567567</v>
+        <v>8140.450189194771</v>
       </c>
       <c r="E80">
-        <v>20529.44104063277</v>
+        <v>20829.52553878582</v>
       </c>
       <c r="F80">
-        <v>23406.59085593838</v>
+        <v>23706.67535409143</v>
       </c>
       <c r="G80">
         <v>1096.2</v>
@@ -7853,37 +7853,37 @@
         <v>1162.7</v>
       </c>
       <c r="M80">
-        <v>4700.043443872426</v>
+        <v>4760.30041110156</v>
       </c>
       <c r="N80">
-        <v>-3537.343443872426</v>
+        <v>-3597.60041110156</v>
       </c>
       <c r="O80">
-        <v>-516.4521428053741</v>
+        <v>-525.2496600208276</v>
       </c>
       <c r="P80">
-        <v>-3020.891301067052</v>
+        <v>-3072.350751080732</v>
       </c>
       <c r="Q80">
-        <v>-2060.791301067052</v>
+        <v>-2112.250751080732</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2101923063284689</v>
+        <v>0.2180205113917294</v>
       </c>
       <c r="T80">
-        <v>3.796589060703671</v>
+        <v>3.977379015975275</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.03611758104519506</v>
+        <v>0.03566039647500271</v>
       </c>
       <c r="W80">
-        <v>0.1935475897261248</v>
+        <v>0.1936393923878195</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2473806920903772</v>
+        <v>0.2442492909246762</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1987594273786406</v>
+        <v>0.2003094273786405</v>
       </c>
       <c r="C81">
-        <v>-14470.02516489666</v>
+        <v>-14847.2403178707</v>
       </c>
       <c r="D81">
-        <v>8140.450189194771</v>
+        <v>8063.31953437379</v>
       </c>
       <c r="E81">
-        <v>20829.52553878582</v>
+        <v>21129.61003693888</v>
       </c>
       <c r="F81">
-        <v>23706.67535409143</v>
+        <v>24006.75985224449</v>
       </c>
       <c r="G81">
         <v>1096.2</v>
@@ -7935,37 +7935,37 @@
         <v>1162.7</v>
       </c>
       <c r="M81">
-        <v>4760.30041110156</v>
+        <v>4820.557378330694</v>
       </c>
       <c r="N81">
-        <v>-3597.60041110156</v>
+        <v>-3657.857378330693</v>
       </c>
       <c r="O81">
-        <v>-525.2496600208276</v>
+        <v>-534.0471772362812</v>
       </c>
       <c r="P81">
-        <v>-3072.350751080732</v>
+        <v>-3123.810201094412</v>
       </c>
       <c r="Q81">
-        <v>-2112.250751080732</v>
+        <v>-2163.710201094412</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2180205113917294</v>
+        <v>0.2266315369613159</v>
       </c>
       <c r="T81">
-        <v>3.977379015975275</v>
+        <v>4.176247966774039</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.03566039647500271</v>
+        <v>0.03521464151906518</v>
       </c>
       <c r="W81">
-        <v>0.1936393923878195</v>
+        <v>0.1937288999829717</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2442492909246762</v>
+        <v>0.2411961747881177</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2003094273786405</v>
+        <v>0.2018594273786406</v>
       </c>
       <c r="C82">
-        <v>-14847.2403178707</v>
+        <v>-15223.00756591358</v>
       </c>
       <c r="D82">
-        <v>8063.31953437379</v>
+        <v>7987.636784483966</v>
       </c>
       <c r="E82">
-        <v>21129.61003693888</v>
+        <v>21429.69453509193</v>
       </c>
       <c r="F82">
-        <v>24006.75985224449</v>
+        <v>24306.84435039754</v>
       </c>
       <c r="G82">
         <v>1096.2</v>
@@ -8017,37 +8017,37 @@
         <v>1162.7</v>
       </c>
       <c r="M82">
-        <v>4820.557378330694</v>
+        <v>4880.814345559827</v>
       </c>
       <c r="N82">
-        <v>-3657.857378330693</v>
+        <v>-3718.114345559826</v>
       </c>
       <c r="O82">
-        <v>-534.0471772362812</v>
+        <v>-542.8446944517345</v>
       </c>
       <c r="P82">
-        <v>-3123.810201094412</v>
+        <v>-3175.269651108092</v>
       </c>
       <c r="Q82">
-        <v>-2163.710201094412</v>
+        <v>-2215.169651108092</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2266315369613159</v>
+        <v>0.2361489862750693</v>
       </c>
       <c r="T82">
-        <v>4.176247966774039</v>
+        <v>4.396050491341094</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.03521464151906518</v>
+        <v>0.03477989285833599</v>
       </c>
       <c r="W82">
-        <v>0.1937288999829717</v>
+        <v>0.1938161975140462</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2411961747881177</v>
+        <v>0.238218444235178</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2018594273786406</v>
+        <v>0.2034094273786405</v>
       </c>
       <c r="C83">
-        <v>-15223.00756591358</v>
+        <v>-15597.36730025126</v>
       </c>
       <c r="D83">
-        <v>7987.636784483966</v>
+        <v>7913.361548299344</v>
       </c>
       <c r="E83">
-        <v>21429.69453509193</v>
+        <v>21729.77903324499</v>
       </c>
       <c r="F83">
-        <v>24306.84435039754</v>
+        <v>24606.9288485506</v>
       </c>
       <c r="G83">
         <v>1096.2</v>
@@ -8099,37 +8099,37 @@
         <v>1162.7</v>
       </c>
       <c r="M83">
-        <v>4880.814345559827</v>
+        <v>4941.07131278896</v>
       </c>
       <c r="N83">
-        <v>-3718.114345559826</v>
+        <v>-3778.37131278896</v>
       </c>
       <c r="O83">
-        <v>-542.8446944517345</v>
+        <v>-551.6422116671881</v>
       </c>
       <c r="P83">
-        <v>-3175.269651108092</v>
+        <v>-3226.729101121772</v>
       </c>
       <c r="Q83">
-        <v>-2215.169651108092</v>
+        <v>-2266.629101121772</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2361489862750693</v>
+        <v>0.2467239299570176</v>
       </c>
       <c r="T83">
-        <v>4.396050491341094</v>
+        <v>4.640275518637822</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.03477989285833599</v>
+        <v>0.03435574782347823</v>
       </c>
       <c r="W83">
-        <v>0.1938161975140462</v>
+        <v>0.1939013658370456</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.238218444235178</v>
+        <v>0.2353133412567002</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2034094273786405</v>
+        <v>0.2049594273786406</v>
       </c>
       <c r="C84">
-        <v>-15597.36730025126</v>
+        <v>-15970.35842359538</v>
       </c>
       <c r="D84">
-        <v>7913.361548299344</v>
+        <v>7840.454923108276</v>
       </c>
       <c r="E84">
-        <v>21729.77903324499</v>
+        <v>22029.86353139805</v>
       </c>
       <c r="F84">
-        <v>24606.9288485506</v>
+        <v>24907.01334670366</v>
       </c>
       <c r="G84">
         <v>1096.2</v>
@@ -8181,37 +8181,37 @@
         <v>1162.7</v>
       </c>
       <c r="M84">
-        <v>4941.07131278896</v>
+        <v>5001.328280018095</v>
       </c>
       <c r="N84">
-        <v>-3778.37131278896</v>
+        <v>-3838.628280018095</v>
       </c>
       <c r="O84">
-        <v>-551.6422116671881</v>
+        <v>-560.4397288826418</v>
       </c>
       <c r="P84">
-        <v>-3226.729101121772</v>
+        <v>-3278.188551135453</v>
       </c>
       <c r="Q84">
-        <v>-2266.629101121772</v>
+        <v>-2318.088551135453</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2467239299570176</v>
+        <v>0.2585429846603716</v>
       </c>
       <c r="T84">
-        <v>4.640275518637822</v>
+        <v>4.913232902087105</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.03435574782347823</v>
+        <v>0.03394182315090619</v>
       </c>
       <c r="W84">
-        <v>0.1939013658370456</v>
+        <v>0.1939844819112981</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2353133412567002</v>
+        <v>0.2324782407596315</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2049594273786406</v>
+        <v>0.2065094273786406</v>
       </c>
       <c r="C85">
-        <v>-15970.35842359538</v>
+        <v>-16342.01841808651</v>
       </c>
       <c r="D85">
-        <v>7840.454923108276</v>
+        <v>7768.879426770202</v>
       </c>
       <c r="E85">
-        <v>22029.86353139805</v>
+        <v>22329.94802955111</v>
       </c>
       <c r="F85">
-        <v>24907.01334670366</v>
+        <v>25207.09784485671</v>
       </c>
       <c r="G85">
         <v>1096.2</v>
@@ -8263,37 +8263,37 @@
         <v>1162.7</v>
       </c>
       <c r="M85">
-        <v>5001.328280018095</v>
+        <v>5061.585247247229</v>
       </c>
       <c r="N85">
-        <v>-3838.628280018095</v>
+        <v>-3898.885247247229</v>
       </c>
       <c r="O85">
-        <v>-560.4397288826418</v>
+        <v>-569.2372460980953</v>
       </c>
       <c r="P85">
-        <v>-3278.188551135453</v>
+        <v>-3329.648001149133</v>
       </c>
       <c r="Q85">
-        <v>-2318.088551135453</v>
+        <v>-2369.548001149133</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2585429846603716</v>
+        <v>0.2718394212016449</v>
       </c>
       <c r="T85">
-        <v>4.913232902087105</v>
+        <v>5.220309958467551</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.03394182315090619</v>
+        <v>0.03353775382768111</v>
       </c>
       <c r="W85">
-        <v>0.1939844819112981</v>
+        <v>0.1940656190314017</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2324782407596315</v>
+        <v>0.2297106426553501</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2065094273786405</v>
+        <v>0.2080594273786405</v>
       </c>
       <c r="C86">
-        <v>-16342.01841808651</v>
+        <v>-16712.38340954947</v>
       </c>
       <c r="D86">
-        <v>7768.879426770205</v>
+        <v>7698.598933460297</v>
       </c>
       <c r="E86">
-        <v>22329.9480295511</v>
+        <v>22630.03252770416</v>
       </c>
       <c r="F86">
-        <v>25207.09784485671</v>
+        <v>25507.18234300976</v>
       </c>
       <c r="G86">
         <v>1096.2</v>
@@ -8345,37 +8345,37 @@
         <v>1162.7</v>
       </c>
       <c r="M86">
-        <v>5061.585247247228</v>
+        <v>5121.842214476361</v>
       </c>
       <c r="N86">
-        <v>-3898.885247247228</v>
+        <v>-3959.142214476361</v>
       </c>
       <c r="O86">
-        <v>-569.2372460980952</v>
+        <v>-578.0347633135486</v>
       </c>
       <c r="P86">
-        <v>-3329.648001149133</v>
+        <v>-3381.107451162812</v>
       </c>
       <c r="Q86">
-        <v>-2369.548001149133</v>
+        <v>-2421.007451162812</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2718394212016447</v>
+        <v>0.286908715948421</v>
       </c>
       <c r="T86">
-        <v>5.220309958467547</v>
+        <v>5.568330622365384</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.03353775382768112</v>
+        <v>0.0331431920179437</v>
       </c>
       <c r="W86">
-        <v>0.1940656190314017</v>
+        <v>0.1941448470427969</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2297106426553501</v>
+        <v>0.2270081645064638</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2080594273786405</v>
+        <v>0.2096094273786405</v>
       </c>
       <c r="C87">
-        <v>-16712.38340954947</v>
+        <v>-17081.48822829234</v>
       </c>
       <c r="D87">
-        <v>7698.598933460297</v>
+        <v>7629.578612870484</v>
       </c>
       <c r="E87">
-        <v>22630.03252770416</v>
+        <v>22930.11702585721</v>
       </c>
       <c r="F87">
-        <v>25507.18234300976</v>
+        <v>25807.26684116282</v>
       </c>
       <c r="G87">
         <v>1096.2</v>
@@ -8427,37 +8427,37 @@
         <v>1162.7</v>
       </c>
       <c r="M87">
-        <v>5121.842214476361</v>
+        <v>5182.099181705495</v>
       </c>
       <c r="N87">
-        <v>-3959.142214476361</v>
+        <v>-4019.399181705494</v>
       </c>
       <c r="O87">
-        <v>-578.0347633135486</v>
+        <v>-586.8322805290021</v>
       </c>
       <c r="P87">
-        <v>-3381.107451162812</v>
+        <v>-3432.566901176492</v>
       </c>
       <c r="Q87">
-        <v>-2421.007451162812</v>
+        <v>-2472.466901176492</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.286908715948421</v>
+        <v>0.304130767087594</v>
       </c>
       <c r="T87">
-        <v>5.568330622365384</v>
+        <v>5.966068523962911</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.0331431920179437</v>
+        <v>0.03275780606424668</v>
       </c>
       <c r="W87">
-        <v>0.1941448470427969</v>
+        <v>0.1942222325422993</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2270081645064638</v>
+        <v>0.2243685346866211</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2096094273786405</v>
+        <v>0.2111594273786405</v>
       </c>
       <c r="C88">
-        <v>-17081.48822829234</v>
+        <v>-17449.36646666392</v>
       </c>
       <c r="D88">
-        <v>7629.578612870484</v>
+        <v>7561.784872651955</v>
       </c>
       <c r="E88">
-        <v>22930.11702585721</v>
+        <v>23230.20152401027</v>
       </c>
       <c r="F88">
-        <v>25807.26684116282</v>
+        <v>26107.35133931588</v>
       </c>
       <c r="G88">
         <v>1096.2</v>
@@ -8509,37 +8509,37 @@
         <v>1162.7</v>
       </c>
       <c r="M88">
-        <v>5182.099181705495</v>
+        <v>5242.356148934628</v>
       </c>
       <c r="N88">
-        <v>-4019.399181705494</v>
+        <v>-4079.656148934628</v>
       </c>
       <c r="O88">
-        <v>-586.8322805290021</v>
+        <v>-595.6297977444557</v>
       </c>
       <c r="P88">
-        <v>-3432.566901176492</v>
+        <v>-3484.026351190173</v>
       </c>
       <c r="Q88">
-        <v>-2472.466901176492</v>
+        <v>-2523.926351190173</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.304130767087594</v>
+        <v>0.3240023645558704</v>
       </c>
       <c r="T88">
-        <v>5.966068523962911</v>
+        <v>6.424996871960058</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.03275780606424668</v>
+        <v>0.03238127955776109</v>
       </c>
       <c r="W88">
-        <v>0.1942222325422993</v>
+        <v>0.1942978390648016</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2243685346866211</v>
+        <v>0.2217895860120622</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2111594273786405</v>
+        <v>0.2127094273786406</v>
       </c>
       <c r="C89">
-        <v>-17449.36646666392</v>
+        <v>-17816.05053356972</v>
       </c>
       <c r="D89">
-        <v>7561.784872651955</v>
+        <v>7495.185303899221</v>
       </c>
       <c r="E89">
-        <v>23230.20152401027</v>
+        <v>23530.28602216333</v>
       </c>
       <c r="F89">
-        <v>26107.35133931588</v>
+        <v>26407.43583746894</v>
       </c>
       <c r="G89">
         <v>1096.2</v>
@@ -8591,37 +8591,37 @@
         <v>1162.7</v>
       </c>
       <c r="M89">
-        <v>5242.356148934628</v>
+        <v>5302.613116163762</v>
       </c>
       <c r="N89">
-        <v>-4079.656148934628</v>
+        <v>-4139.913116163762</v>
       </c>
       <c r="O89">
-        <v>-595.6297977444557</v>
+        <v>-604.4273149599092</v>
       </c>
       <c r="P89">
-        <v>-3484.026351190173</v>
+        <v>-3535.485801203852</v>
       </c>
       <c r="Q89">
-        <v>-2523.926351190173</v>
+        <v>-2575.385801203852</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3240023645558704</v>
+        <v>0.3471858949355264</v>
       </c>
       <c r="T89">
-        <v>6.424996871960058</v>
+        <v>6.960413277956731</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.03238127955776109</v>
+        <v>0.03201331047187744</v>
       </c>
       <c r="W89">
-        <v>0.1942978390648016</v>
+        <v>0.194371727257247</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2217895860120622</v>
+        <v>0.2192692498073798</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2127094273786406</v>
+        <v>0.2142594273786405</v>
       </c>
       <c r="C90">
-        <v>-17816.05053356972</v>
+        <v>-18181.57170613212</v>
       </c>
       <c r="D90">
-        <v>7495.185303899221</v>
+        <v>7429.748629489875</v>
       </c>
       <c r="E90">
-        <v>23530.28602216333</v>
+        <v>23830.37052031638</v>
       </c>
       <c r="F90">
-        <v>26407.43583746894</v>
+        <v>26707.52033562199</v>
       </c>
       <c r="G90">
         <v>1096.2</v>
@@ -8673,37 +8673,37 @@
         <v>1162.7</v>
       </c>
       <c r="M90">
-        <v>5302.613116163762</v>
+        <v>5362.870083392896</v>
       </c>
       <c r="N90">
-        <v>-4139.913116163762</v>
+        <v>-4200.170083392895</v>
       </c>
       <c r="O90">
-        <v>-604.4273149599092</v>
+        <v>-613.2248321753627</v>
       </c>
       <c r="P90">
-        <v>-3535.485801203852</v>
+        <v>-3586.945251217533</v>
       </c>
       <c r="Q90">
-        <v>-2575.385801203852</v>
+        <v>-2626.845251217533</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3471858949355264</v>
+        <v>0.3745846126569379</v>
       </c>
       <c r="T90">
-        <v>6.960413277956731</v>
+        <v>7.593178121407343</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.03201331047187744</v>
+        <v>0.03165361035421589</v>
       </c>
       <c r="W90">
-        <v>0.194371727257247</v>
+        <v>0.1944439550408734</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2192692498073798</v>
+        <v>0.2168055503713419</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2142594273786405</v>
+        <v>0.2158094273786406</v>
       </c>
       <c r="C91">
-        <v>-18181.57170613212</v>
+        <v>-18545.96017866798</v>
       </c>
       <c r="D91">
-        <v>7429.748629489875</v>
+        <v>7365.444655107071</v>
       </c>
       <c r="E91">
-        <v>23830.37052031638</v>
+        <v>24130.45501846944</v>
       </c>
       <c r="F91">
-        <v>26707.52033562199</v>
+        <v>27007.60483377505</v>
       </c>
       <c r="G91">
         <v>1096.2</v>
@@ -8755,37 +8755,37 @@
         <v>1162.7</v>
       </c>
       <c r="M91">
-        <v>5362.870083392896</v>
+        <v>5423.12705062203</v>
       </c>
       <c r="N91">
-        <v>-4200.170083392895</v>
+        <v>-4260.427050622029</v>
       </c>
       <c r="O91">
-        <v>-613.2248321753627</v>
+        <v>-622.0223493908162</v>
       </c>
       <c r="P91">
-        <v>-3586.945251217533</v>
+        <v>-3638.404701231213</v>
       </c>
       <c r="Q91">
-        <v>-2626.845251217533</v>
+        <v>-2678.304701231213</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3745846126569379</v>
+        <v>0.4074630739226317</v>
       </c>
       <c r="T91">
-        <v>7.593178121407343</v>
+        <v>8.352495933548077</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.03165361035421589</v>
+        <v>0.03130190357250238</v>
       </c>
       <c r="W91">
-        <v>0.1944439550408734</v>
+        <v>0.1945145777626415</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2168055503713419</v>
+        <v>0.2143965998116603</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2158094273786406</v>
+        <v>0.2173594273786405</v>
       </c>
       <c r="C92">
-        <v>-18545.96017866798</v>
+        <v>-18909.24510914455</v>
       </c>
       <c r="D92">
-        <v>7365.444655107071</v>
+        <v>7302.244222783552</v>
       </c>
       <c r="E92">
-        <v>24130.45501846944</v>
+        <v>24430.5395166225</v>
       </c>
       <c r="F92">
-        <v>27007.60483377505</v>
+        <v>27307.6893319281</v>
       </c>
       <c r="G92">
         <v>1096.2</v>
@@ -8837,37 +8837,37 @@
         <v>1162.7</v>
       </c>
       <c r="M92">
-        <v>5423.12705062203</v>
+        <v>5483.384017851164</v>
       </c>
       <c r="N92">
-        <v>-4260.427050622029</v>
+        <v>-4320.684017851163</v>
       </c>
       <c r="O92">
-        <v>-622.0223493908162</v>
+        <v>-630.8198666062698</v>
       </c>
       <c r="P92">
-        <v>-3638.404701231213</v>
+        <v>-3689.864151244893</v>
       </c>
       <c r="Q92">
-        <v>-2678.304701231213</v>
+        <v>-2729.764151244893</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4074630739226317</v>
+        <v>0.4476478599140353</v>
       </c>
       <c r="T92">
-        <v>8.352495933548077</v>
+        <v>9.280551037275643</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.03130190357250238</v>
+        <v>0.03095792661016719</v>
       </c>
       <c r="W92">
-        <v>0.1945145777626415</v>
+        <v>0.1945836483366784</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2143965998116603</v>
+        <v>0.2120405932203233</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2173594273786405</v>
+        <v>0.2189094273786406</v>
       </c>
       <c r="C93">
-        <v>-18909.24510914455</v>
+        <v>-19271.45466326411</v>
       </c>
       <c r="D93">
-        <v>7302.244222783552</v>
+        <v>7240.119166817056</v>
       </c>
       <c r="E93">
-        <v>24430.5395166225</v>
+        <v>24730.62401477555</v>
       </c>
       <c r="F93">
-        <v>27307.6893319281</v>
+        <v>27607.77383008116</v>
       </c>
       <c r="G93">
         <v>1096.2</v>
@@ -8919,37 +8919,37 @@
         <v>1162.7</v>
       </c>
       <c r="M93">
-        <v>5483.384017851164</v>
+        <v>5543.640985080297</v>
       </c>
       <c r="N93">
-        <v>-4320.684017851163</v>
+        <v>-4380.940985080297</v>
       </c>
       <c r="O93">
-        <v>-630.8198666062698</v>
+        <v>-639.6173838217233</v>
       </c>
       <c r="P93">
-        <v>-3689.864151244893</v>
+        <v>-3741.323601258573</v>
       </c>
       <c r="Q93">
-        <v>-2729.764151244893</v>
+        <v>-2781.223601258574</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4476478599140353</v>
+        <v>0.4978788424032898</v>
       </c>
       <c r="T93">
-        <v>9.280551037275643</v>
+        <v>10.4406199169351</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.03095792661016719</v>
+        <v>0.03062142740788277</v>
       </c>
       <c r="W93">
-        <v>0.1945836483366784</v>
+        <v>0.1946512173764972</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2120405932203233</v>
+        <v>0.2097358041635807</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2189094273786406</v>
+        <v>0.2204594273786405</v>
       </c>
       <c r="C94">
-        <v>-19271.45466326411</v>
+        <v>-19632.61605631711</v>
       </c>
       <c r="D94">
-        <v>7240.119166817056</v>
+        <v>7179.042271917108</v>
       </c>
       <c r="E94">
-        <v>24730.62401477555</v>
+        <v>25030.70851292861</v>
       </c>
       <c r="F94">
-        <v>27607.77383008116</v>
+        <v>27907.85832823422</v>
       </c>
       <c r="G94">
         <v>1096.2</v>
@@ -9001,37 +9001,37 @@
         <v>1162.7</v>
       </c>
       <c r="M94">
-        <v>5543.640985080297</v>
+        <v>5603.897952309431</v>
       </c>
       <c r="N94">
-        <v>-4380.940985080297</v>
+        <v>-4441.197952309431</v>
       </c>
       <c r="O94">
-        <v>-639.6173838217233</v>
+        <v>-648.4149010371768</v>
       </c>
       <c r="P94">
-        <v>-3741.323601258573</v>
+        <v>-3792.783051272254</v>
       </c>
       <c r="Q94">
-        <v>-2781.223601258574</v>
+        <v>-2832.683051272254</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4978788424032898</v>
+        <v>0.5624615341751883</v>
       </c>
       <c r="T94">
-        <v>10.4406199169351</v>
+        <v>11.93213704792583</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.03062142740788277</v>
+        <v>0.03029216474758295</v>
       </c>
       <c r="W94">
-        <v>0.1946512173764972</v>
+        <v>0.1947173333186853</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2097358041635807</v>
+        <v>0.207480580462897</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2204594273786405</v>
+        <v>0.2220094273786405</v>
       </c>
       <c r="C95">
-        <v>-19632.61605631711</v>
+        <v>-19992.75559293478</v>
       </c>
       <c r="D95">
-        <v>7179.042271917108</v>
+        <v>7118.987233452489</v>
       </c>
       <c r="E95">
-        <v>25030.70851292861</v>
+        <v>25330.79301108166</v>
       </c>
       <c r="F95">
-        <v>27907.85832823422</v>
+        <v>28207.94282638727</v>
       </c>
       <c r="G95">
         <v>1096.2</v>
@@ -9083,37 +9083,37 @@
         <v>1162.7</v>
       </c>
       <c r="M95">
-        <v>5603.897952309431</v>
+        <v>5664.154919538564</v>
       </c>
       <c r="N95">
-        <v>-4441.197952309431</v>
+        <v>-4501.454919538564</v>
       </c>
       <c r="O95">
-        <v>-648.4149010371768</v>
+        <v>-657.2124182526303</v>
       </c>
       <c r="P95">
-        <v>-3792.783051272254</v>
+        <v>-3844.242501285934</v>
       </c>
       <c r="Q95">
-        <v>-2832.683051272254</v>
+        <v>-2884.142501285934</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5624615341751883</v>
+        <v>0.6485717898710534</v>
       </c>
       <c r="T95">
-        <v>11.93213704792583</v>
+        <v>13.92082655591348</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.03029216474758295</v>
+        <v>0.02996990767580015</v>
       </c>
       <c r="W95">
-        <v>0.1947173333186853</v>
+        <v>0.1947820425386994</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.207480580462897</v>
+        <v>0.2052733402452065</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2220094273786405</v>
+        <v>0.2235594273786405</v>
       </c>
       <c r="C96">
-        <v>-19992.75559293478</v>
+        <v>-20351.89870486293</v>
       </c>
       <c r="D96">
-        <v>7118.987233452489</v>
+        <v>7059.928619677399</v>
       </c>
       <c r="E96">
-        <v>25330.79301108166</v>
+        <v>25630.87750923472</v>
       </c>
       <c r="F96">
-        <v>28207.94282638727</v>
+        <v>28508.02732454033</v>
       </c>
       <c r="G96">
         <v>1096.2</v>
@@ -9165,37 +9165,37 @@
         <v>1162.7</v>
       </c>
       <c r="M96">
-        <v>5664.154919538564</v>
+        <v>5724.411886767698</v>
       </c>
       <c r="N96">
-        <v>-4501.454919538564</v>
+        <v>-4561.711886767698</v>
       </c>
       <c r="O96">
-        <v>-657.2124182526303</v>
+        <v>-666.0099354680839</v>
       </c>
       <c r="P96">
-        <v>-3844.242501285934</v>
+        <v>-3895.701951299614</v>
       </c>
       <c r="Q96">
-        <v>-2884.142501285934</v>
+        <v>-2935.601951299614</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6485717898710534</v>
+        <v>0.7691261478452642</v>
       </c>
       <c r="T96">
-        <v>13.92082655591348</v>
+        <v>16.70499186709618</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.02996990767580015</v>
+        <v>0.02965443496342331</v>
       </c>
       <c r="W96">
-        <v>0.1947820425386994</v>
+        <v>0.1948453894593446</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2052733402452065</v>
+        <v>0.2031125682426254</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2235594273786405</v>
+        <v>0.2251094273786405</v>
       </c>
       <c r="C97">
-        <v>-20351.89870486293</v>
+        <v>-20710.06998687099</v>
       </c>
       <c r="D97">
-        <v>7059.928619677399</v>
+        <v>7001.841835822394</v>
       </c>
       <c r="E97">
-        <v>25630.87750923472</v>
+        <v>25930.96200738778</v>
       </c>
       <c r="F97">
-        <v>28508.02732454033</v>
+        <v>28808.11182269339</v>
       </c>
       <c r="G97">
         <v>1096.2</v>
@@ -9247,37 +9247,37 @@
         <v>1162.7</v>
       </c>
       <c r="M97">
-        <v>5724.411886767698</v>
+        <v>5784.668853996833</v>
       </c>
       <c r="N97">
-        <v>-4561.711886767698</v>
+        <v>-4621.968853996832</v>
       </c>
       <c r="O97">
-        <v>-666.0099354680839</v>
+        <v>-674.8074526835375</v>
       </c>
       <c r="P97">
-        <v>-3895.701951299614</v>
+        <v>-3947.161401313294</v>
       </c>
       <c r="Q97">
-        <v>-2935.601951299614</v>
+        <v>-2987.061401313294</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7691261478452642</v>
+        <v>0.9499576848065807</v>
       </c>
       <c r="T97">
-        <v>16.70499186709618</v>
+        <v>20.88123983387023</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.02965443496342331</v>
+        <v>0.02934553459922098</v>
       </c>
       <c r="W97">
-        <v>0.1948453894593446</v>
+        <v>0.1949074166524764</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2031125682426254</v>
+        <v>0.2009968123234315</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2251094273786405</v>
+        <v>0.2607650426217946</v>
       </c>
       <c r="C98">
-        <v>-20710.06998687099</v>
+        <v>-22124.46555969714</v>
       </c>
       <c r="D98">
-        <v>7001.841835822394</v>
+        <v>5887.530761149304</v>
       </c>
       <c r="E98">
-        <v>25930.96200738777</v>
+        <v>26231.04650554083</v>
       </c>
       <c r="F98">
-        <v>28808.11182269338</v>
+        <v>29108.19632084644</v>
       </c>
       <c r="G98">
         <v>1096.2</v>
@@ -9329,45 +9329,45 @@
         <v>1162.7</v>
       </c>
       <c r="M98">
-        <v>5784.668853996832</v>
+        <v>6863.712692455591</v>
       </c>
       <c r="N98">
-        <v>-4621.968853996832</v>
+        <v>-5701.01269245559</v>
       </c>
       <c r="O98">
-        <v>-674.8074526835375</v>
+        <v>-832.3478530985161</v>
       </c>
       <c r="P98">
-        <v>-3947.161401313294</v>
+        <v>-4868.664839357074</v>
       </c>
       <c r="Q98">
-        <v>-2987.061401313294</v>
+        <v>-3908.564839357074</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9499576848065782</v>
+        <v>1.256530754513905</v>
       </c>
       <c r="T98">
-        <v>20.88123983387017</v>
+        <v>27.96144929593315</v>
       </c>
       <c r="U98">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02934553459922098</v>
+        <v>0.02473212496009475</v>
       </c>
       <c r="W98">
-        <v>0.1949074166524764</v>
+        <v>0.2299681649344097</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.2009968123234314</v>
+        <v>0.1693981161650326</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2607650426217946</v>
+        <v>0.2626650426217945</v>
       </c>
       <c r="C99">
-        <v>-22124.46555969714</v>
+        <v>-22474.05921293033</v>
       </c>
       <c r="D99">
-        <v>5887.530761149304</v>
+        <v>5838.021606069163</v>
       </c>
       <c r="E99">
-        <v>26231.04650554083</v>
+        <v>26531.13100369388</v>
       </c>
       <c r="F99">
-        <v>29108.19632084644</v>
+        <v>29408.28081899949</v>
       </c>
       <c r="G99">
         <v>1096.2</v>
@@ -9411,37 +9411,37 @@
         <v>1162.7</v>
       </c>
       <c r="M99">
-        <v>6863.712692455591</v>
+        <v>6934.472617120081</v>
       </c>
       <c r="N99">
-        <v>-5701.01269245559</v>
+        <v>-5771.772617120081</v>
       </c>
       <c r="O99">
-        <v>-832.3478530985161</v>
+        <v>-842.6788020995318</v>
       </c>
       <c r="P99">
-        <v>-4868.664839357074</v>
+        <v>-4929.093815020549</v>
       </c>
       <c r="Q99">
-        <v>-3908.564839357074</v>
+        <v>-3968.993815020549</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.256530754513905</v>
+        <v>1.861896131770857</v>
       </c>
       <c r="T99">
-        <v>27.96144929593315</v>
+        <v>41.94217394389971</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02473212496009475</v>
+        <v>0.02447975633805296</v>
       </c>
       <c r="W99">
-        <v>0.2299681649344097</v>
+        <v>0.2300276734554871</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1693981161650326</v>
+        <v>0.1676695639592668</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2626650426217945</v>
+        <v>0.2645650426217945</v>
       </c>
       <c r="C100">
-        <v>-22474.05921293033</v>
+        <v>-22822.82714948608</v>
       </c>
       <c r="D100">
-        <v>5838.021606069163</v>
+        <v>5789.338167666471</v>
       </c>
       <c r="E100">
-        <v>26531.13100369388</v>
+        <v>26831.21550184694</v>
       </c>
       <c r="F100">
-        <v>29408.28081899949</v>
+        <v>29708.36531715255</v>
       </c>
       <c r="G100">
         <v>1096.2</v>
@@ -9493,37 +9493,37 @@
         <v>1162.7</v>
       </c>
       <c r="M100">
-        <v>6934.472617120081</v>
+        <v>7005.232541784572</v>
       </c>
       <c r="N100">
-        <v>-5771.772617120081</v>
+        <v>-5842.532541784572</v>
       </c>
       <c r="O100">
-        <v>-842.6788020995318</v>
+        <v>-853.0097511005475</v>
       </c>
       <c r="P100">
-        <v>-4929.093815020549</v>
+        <v>-4989.522790684025</v>
       </c>
       <c r="Q100">
-        <v>-3968.993815020549</v>
+        <v>-4029.422790684025</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.861896131770857</v>
+        <v>3.677992263541714</v>
       </c>
       <c r="T100">
-        <v>41.94217394389971</v>
+        <v>83.88434788779942</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02447975633805296</v>
+        <v>0.02423248607201203</v>
       </c>
       <c r="W100">
-        <v>0.2300276734554871</v>
+        <v>0.2300859797842196</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1676695639592668</v>
+        <v>0.1659759320000823</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2645650426217945</v>
-      </c>
-      <c r="C101">
-        <v>-22822.82714948608</v>
-      </c>
-      <c r="D101">
-        <v>5789.338167666471</v>
-      </c>
-      <c r="E101">
-        <v>26831.21550184694</v>
-      </c>
-      <c r="F101">
-        <v>29708.36531715255</v>
-      </c>
-      <c r="G101">
-        <v>1096.2</v>
-      </c>
-      <c r="H101">
-        <v>27131.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2122.8</v>
-      </c>
-      <c r="K101">
-        <v>960.1</v>
-      </c>
-      <c r="L101">
-        <v>1162.7</v>
-      </c>
-      <c r="M101">
-        <v>7005.232541784572</v>
-      </c>
-      <c r="N101">
-        <v>-5842.532541784572</v>
-      </c>
-      <c r="O101">
-        <v>-853.0097511005475</v>
-      </c>
-      <c r="P101">
-        <v>-4989.522790684025</v>
-      </c>
-      <c r="Q101">
-        <v>-4029.422790684025</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.677992263541714</v>
-      </c>
-      <c r="T101">
-        <v>83.88434788779942</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02423248607201203</v>
-      </c>
-      <c r="W101">
-        <v>0.2300859797842196</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1659759320000823</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
